--- a/nica-apify/calendario/calendario-semana-2026-10-06.xlsx
+++ b/nica-apify/calendario/calendario-semana-2026-10-06.xlsx
@@ -9,12 +9,13 @@
   <sheets>
     <sheet name="Cómo leer" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Calendario" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mi semana" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Podcast y YouTube" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Querido Ex" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Guion por partes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mi semana" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Podcast y YouTube" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Querido Ex" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario'!$A$1:$Y$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario'!$A$1:$AH$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -567,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -590,115 +591,127 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Una fila = una pieza (18). El mismo video va a las 4 redes de la columna PLATAFORMAS.</t>
+          <t>Una fila = una pieza (18). TÍTULO DEL VIDEO es el nombre de cada pieza. El mismo video va a las 4 redes de la columna PLATAFORMAS. Ahí está todo lo del guion: audiencia, copy de cada red, simulación y nota.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Guion completo por tiempos</t>
+          <t>Guion por partes</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Todo lo que dices, con el segundo en que va cada parte: GANCHO → GUARDAR Y COMPARTIR → DOLOR → HACKEO → REVELACIÓN → COMENTA → CTA. Los tiempos se calculan a ritmo cómodo (unas 150 palabras por minuto) más 6 segundos para que hagan el hackeo contigo.</t>
+          <t>El guion original separado en sus 8 partes (HOOK, GUARDA, PROBLEMA Y SÍNTOMA, REENCUADRE, PUENTE, MICROHERRAMIENTA, REVELACIÓN, CTA), por si quieres verlo así.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Hora (Monterrey)</t>
+          <t>Guion completo por tiempos</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Sale de tus 40 TikToks: de 18 a 21 h rinden 6.3x tu mediana (7 videos) y de 10 a 13 h, 1.6x (5 videos). De 22 a 5 h, donde más publicas (14 videos), rinden 0.5x. Son pocos videos: es una señal, no una certeza. Instagram, Facebook y YouTube no tienen dato propio todavía.</t>
+          <t>Todo lo que dices, con el segundo en que va cada parte: GANCHO → GUARDAR Y COMPARTIR → DOLOR → HACKEO → REVELACIÓN → COMENTA → CTA. Los tiempos se calculan a ritmo cómodo (unas 150 palabras por minuto) más 6 segundos para que hagan el hackeo contigo.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Copy out</t>
+          <t>Hora (Monterrey)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>El texto que pegas al publicar en TikTok, Instagram y Facebook, ya con hashtags. YouTube Shorts lleva su título aparte.</t>
+          <t>Sale de tus 40 TikToks: de 18 a 21 h rinden 6.3x tu mediana (7 videos) y de 10 a 13 h, 1.6x (5 videos). De 22 a 5 h, donde más publicas (14 videos), rinden 0.5x. Son pocos videos: es una señal, no una certeza. Instagram, Facebook y YouTube no tienen dato propio todavía.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Hashtags</t>
+          <t>Copy out</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5 por pieza: #mabradiante + 2 del problema + 1 de tu nicho + #mty (para ser la referente en Monterrey y México). Quitamos #teamwork, #following y #bdtiktokofficial: no tienen relación con tu tema.</t>
+          <t>El texto que pegas al publicar en TikTok, Instagram y Facebook, ya con hashtags. YouTube Shorts lleva su título aparte.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Emoción</t>
+          <t>Hashtags</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>La emoción que busca el gancho: sorpresa, alivio, identificación o curiosidad.</t>
+          <t>5 por pieza: #mabradiante + 2 del problema + 1 de tu nicho + #mty (para ser la referente en Monterrey y México). Quitamos #teamwork, #following y #bdtiktokofficial: no tienen relación con tu tema.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Rendimiento esperado</t>
+          <t>Emoción</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>La meta de cada pieza contra tus propios números. No es una predicción: es la vara para medir.</t>
+          <t>La emoción que busca el gancho: sorpresa, alivio, identificación o curiosidad.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Patrón</t>
+          <t>Rendimiento esperado</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Qué fórmula viral usa la pieza. En la rutina semanal vemos cuál te funcionó y repetimos esa.</t>
+          <t>La meta de cada pieza contra tus propios números. No es una predicción: es la vara para medir.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Celdas amarillas</t>
+          <t>Patrón</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Las llenas tú: ¿Grabado?, ¿Publicado? y tus números reales.</t>
+          <t>Qué fórmula viral usa la pieza. En la rutina semanal vemos cuál te funcionó y repetimos esa.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>Celdas amarillas</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Las llenas tú: ¿Grabado?, ¿Publicado?, tus números reales y si coincidió con la simulación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>Pestañas</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Calendario · Mi semana · Podcast y YouTube · Querido Ex (los 8 audios completos para leer y grabar).</t>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Calendario · Guion por partes · Mi semana · Podcast y YouTube · Querido Ex (los 8 audios completos para leer y grabar).</t>
         </is>
       </c>
     </row>
@@ -713,34 +726,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:AH22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="45" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="36" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="36" customWidth="1" min="18" max="18"/>
-    <col width="42" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
+    <col width="36" customWidth="1" min="23" max="23"/>
+    <col width="42" customWidth="1" min="24" max="24"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="30" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -761,112 +783,157 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
+          <t>PIEZA</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>TÍTULO DEL VIDEO</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Nombre interno</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
           <t>PLATAFORMAS</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>PIEZA</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>TEMA (problema)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Audiencia</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>TIPO DE HOOK</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>EMOCIÓN</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>GUION COMPLETO POR TIEMPOS (lo que dices)</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>DURACIÓN</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>FORMATO</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>CTA: comenta…</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>COPY OUT (TikTok, Instagram y Facebook)</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>COPY OUT · TikTok</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>COPY OUT · Instagram Reels</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>COPY OUT · Facebook Reels</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Título YouTube Shorts</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>HASHTAGS</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>RENDIMIENTO ESPERADO</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>PATRÓN viral que usa</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>Por qué en este orden y a esta hora</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
-        <is>
-          <t>Calificación vs patrones</t>
-        </is>
-      </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>Simulación (calificación vs patrones, no predice vistas)</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
+          <t>Calificación</t>
+        </is>
+      </c>
+      <c r="AA1" s="4" t="inlineStr">
+        <is>
+          <t>Nota de la pieza</t>
+        </is>
+      </c>
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>¿Grabado?</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>¿Publicado?</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="AD1" s="4" t="inlineStr">
         <is>
           <t>Vistas reales</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="AE1" s="4" t="inlineStr">
+        <is>
+          <t>Likes reales</t>
+        </is>
+      </c>
+      <c r="AF1" s="4" t="inlineStr">
         <is>
           <t>Comentarios reales</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="AG1" s="4" t="inlineStr">
         <is>
           <t>Compartidos reales</t>
+        </is>
+      </c>
+      <c r="AH1" s="4" t="inlineStr">
+        <is>
+          <t>¿Coincidió con la simulación?</t>
         </is>
       </c>
     </row>
@@ -883,35 +950,50 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>12:30 (ya pasó: ver pendiente)</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>MAR-1</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>No era ansiedad: era una mente sin dirección</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Martes 06 · Pieza 1 · Ansiedad · mente que no para</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>MAR-1</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Ansiedad · mente que no para</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>A y B</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>G1 · Confesión + reencuadre</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Sorpresa: "nunca lo había visto así"</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>[0:00–0:07] GANCHO: "Durante años creí que tenía ansiedad. Lo que tenía era una mente que nadie me enseñó a dirigir."
 [0:07–0:14] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien cuya mente no se apaga."
@@ -922,67 +1004,99 @@
 [1:09–1:13] CTA: "Sígueme para más hackeos de tu mente y la Matrix."</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>≈ 1:13 min (73 s)</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>MENTE</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>Sin venta (conexión)</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="Q2" s="5" t="inlineStr">
         <is>
           <t>Durante años creí que tenía ansiedad… 🧠 Guarda este video y compártelo con alguien cuya mente no para. Comenta MENTE 👇
 #mabradiante #ansiedad #calmamental #hackeatumente #mty</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>Durante años creí que tenía ansiedad… 🧠 Guarda este video y compártelo con alguien cuya mente no para. Comenta MENTE 👇
+#mabradiante #ansiedad #calmamental #hackeatumente #mty</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Durante años creí que tenía ansiedad… 🧠 Guarda este video y compártelo con alguien cuya mente no para. Comenta MENTE 👇
+#mabradiante #ansiedad #calmamental #hackeatumente #mty</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
         <is>
           <t>No era ansiedad: era una mente sin dirección #mabradiante #ansiedad #calmamental #hackeatumente #mty #shorts</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="U2" s="5" t="inlineStr">
         <is>
           <t>#mabradiante #ansiedad #calmamental #hackeatumente #mty</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="V2" s="5" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="W2" s="5" t="inlineStr">
         <is>
           <t>Romper creencia: "No es que… es que…" (el gancho más repetido en los virales)</t>
         </is>
       </c>
-      <c r="S2" s="5" t="inlineStr">
+      <c r="X2" s="5" t="inlineStr">
         <is>
           <t>Pieza 1 abre el tema del día (rompe una creencia). Mediodía: tus TikToks de 10 a 13 h rinden 1.6x tu mediana (5 videos).</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr">
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U2" s="7" t="inlineStr"/>
-      <c r="V2" s="7" t="inlineStr"/>
-      <c r="W2" s="7" t="inlineStr"/>
-      <c r="X2" s="7" t="inlineStr"/>
-      <c r="Y2" s="7" t="inlineStr"/>
+      <c r="AA2" s="5" t="inlineStr">
+        <is>
+          <t>Pieza de historia personal (TDAH): sin venta.</t>
+        </is>
+      </c>
+      <c r="AB2" s="7" t="inlineStr"/>
+      <c r="AC2" s="7" t="inlineStr"/>
+      <c r="AD2" s="7" t="inlineStr"/>
+      <c r="AE2" s="7" t="inlineStr"/>
+      <c r="AF2" s="7" t="inlineStr"/>
+      <c r="AG2" s="7" t="inlineStr"/>
+      <c r="AH2" s="7" t="inlineStr"/>
     </row>
     <row r="3" ht="330" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -997,35 +1111,50 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>18:30 (ya pasó: ver pendiente)</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>MAR-2</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Respiración de 60 segundos para la ansiedad</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Martes 06 · Pieza 2 · Ansiedad · ataque en el cuerpo</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>MAR-2</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Ansiedad · ataque en el cuerpo</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>G2 · Promesa práctica</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Alivio: "algo que puedo hacer ya"</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>[0:00–0:05] GANCHO: "Haz esto 60 segundos cuando sientas que la ansiedad te sube al pecho."
 [0:05–0:12] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien cuya mente no se apaga."
@@ -1036,67 +1165,99 @@
 [1:03–1:07] CTA: "Sígueme para más hackeos de tu mente y la Matrix."</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>≈ 1:07 min (67 s)</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>CALMA</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>Sin venta (conexión)</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>60 segundos para bajar la ansiedad desde el cuerpo 🫁 Guárdalo antes de que se te pierda. Comenta CALMA 👇
 #mabradiante #ansiedad #calmamental #hackeatumente #mty</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>60 segundos para bajar la ansiedad desde el cuerpo 🫁 Guárdalo antes de que se te pierda. Comenta CALMA 👇
+#mabradiante #ansiedad #calmamental #hackeatumente #mty</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>60 segundos para bajar la ansiedad desde el cuerpo 🫁 Guárdalo antes de que se te pierda. Comenta CALMA 👇
+#mabradiante #ansiedad #calmamental #hackeatumente #mty</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>Respiración de 60 segundos para la ansiedad #mabradiante #ansiedad #calmamental #hackeatumente #mty #shorts</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>#mabradiante #ansiedad #calmamental #hackeatumente #mty</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>Algo para usar ya: decreto, respiración o ritual (tu viral de 2.2M y tus 4 más vistos)</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="X3" s="5" t="inlineStr">
         <is>
           <t>Pieza 2 es la herramienta, la más compartible. Tu mejor horario: de 18 a 21 h tus TikToks rinden 6.3x tu mediana (7 videos).</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U3" s="7" t="inlineStr"/>
-      <c r="V3" s="7" t="inlineStr"/>
-      <c r="W3" s="7" t="inlineStr"/>
-      <c r="X3" s="7" t="inlineStr"/>
-      <c r="Y3" s="7" t="inlineStr"/>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB3" s="7" t="inlineStr"/>
+      <c r="AC3" s="7" t="inlineStr"/>
+      <c r="AD3" s="7" t="inlineStr"/>
+      <c r="AE3" s="7" t="inlineStr"/>
+      <c r="AF3" s="7" t="inlineStr"/>
+      <c r="AG3" s="7" t="inlineStr"/>
+      <c r="AH3" s="7" t="inlineStr"/>
     </row>
     <row r="4" ht="330" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -1111,35 +1272,50 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>20:30 (ya pasó: ver pendiente)</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>MAR-3</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Por qué tu mente se acelera al dormir</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Martes 06 · Pieza 3 · Ansiedad · insomnio</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>MAR-3</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Ansiedad · insomnio</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>A y B</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>G4 · Pregunta-dolor</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Identificación: "eso me pasa a mí"</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>[0:00–0:06] GANCHO: "¿Por qué tu mente se acelera justo cuando por fin te acuestas a dormir?"
 [0:06–0:13] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien cuya mente no se apaga."
@@ -1150,67 +1326,99 @@
 [1:03–1:12] CTA: "Si tu mente no te deja dormir, en Querida Ansiedad te doy la auditoría mental y los audios para bajar su velocidad."</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>≈ 1:12 min (72 s)</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>DORMIR</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>Querida Ansiedad · $399</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>¿Tu mente se prende justo cuando te acuestas? 🌙 Guarda este hackeo para esta noche. Comenta DORMIR 👇
 #mabradiante #ansiedad #calmamental #hackeatumente #mty</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>¿Tu mente se prende justo cuando te acuestas? 🌙 Guarda este hackeo para esta noche. Comenta DORMIR 👇
+#mabradiante #ansiedad #calmamental #hackeatumente #mty</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>¿Tu mente se prende justo cuando te acuestas? 🌙 Guarda este hackeo para esta noche. Comenta DORMIR 👇
+#mabradiante #ansiedad #calmamental #hackeatumente #mty</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>Por qué tu mente se acelera al dormir #mabradiante #ansiedad #calmamental #hackeatumente #mty #shorts</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>#mabradiante #ansiedad #calmamental #hackeatumente #mty</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="W4" s="5" t="inlineStr">
         <is>
           <t>Pregunta-dolor: nombrar lo que ella siente en sus palabras</t>
         </is>
       </c>
-      <c r="S4" s="5" t="inlineStr">
+      <c r="X4" s="5" t="inlineStr">
         <is>
           <t>Pieza 3 cierra con la venta, cuando ya calentaste el tema con las 2 anteriores. Sigue en tu mejor franja (18 a 21 h).</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U4" s="7" t="inlineStr"/>
-      <c r="V4" s="7" t="inlineStr"/>
-      <c r="W4" s="7" t="inlineStr"/>
-      <c r="X4" s="7" t="inlineStr"/>
-      <c r="Y4" s="7" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>Pieza de venta del día (1 de 3).</t>
+        </is>
+      </c>
+      <c r="AB4" s="7" t="inlineStr"/>
+      <c r="AC4" s="7" t="inlineStr"/>
+      <c r="AD4" s="7" t="inlineStr"/>
+      <c r="AE4" s="7" t="inlineStr"/>
+      <c r="AF4" s="7" t="inlineStr"/>
+      <c r="AG4" s="7" t="inlineStr"/>
+      <c r="AH4" s="7" t="inlineStr"/>
     </row>
     <row r="5" ht="330" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
@@ -1228,32 +1436,47 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>MIÉ-1</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Por qué repites la misma relación</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Miércoles 07 · Pieza 1 · Relaciones · repetir la misma historia</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>MIÉ-1</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Relaciones · repetir la misma historia</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>G1 · Reencuadre</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>Sorpresa: "nunca lo había visto así"</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>[0:00–0:08] GANCHO: "No es que siempre te toque la persona equivocada. Es que tu sistema reconoce como 'amor' lo que ya conoce."
 [0:08–0:17] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con esa amiga que siempre repite la misma historia en el amor."
@@ -1264,67 +1487,99 @@
 [1:06–1:10] CTA: "Sígueme para más hackeos de tu mente y la Matrix."</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>≈ 1:10 min (70 s)</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="O5" s="8" t="inlineStr">
         <is>
           <t>PATRÓN</t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr">
+      <c r="P5" s="8" t="inlineStr">
         <is>
           <t>Sin venta (conexión)</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="Q5" s="8" t="inlineStr">
         <is>
           <t>¿Siempre te toca la persona equivocada? 💔 Guárdalo y compártelo con tu amiga que repite la historia. Comenta PATRÓN 👇
 #mabradiante #relaciones #amorpropio #dependenciaemocional #mty</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>¿Siempre te toca la persona equivocada? 💔 Guárdalo y compártelo con tu amiga que repite la historia. Comenta PATRÓN 👇
+#mabradiante #relaciones #amorpropio #dependenciaemocional #mty</t>
+        </is>
+      </c>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t>¿Siempre te toca la persona equivocada? 💔 Guárdalo y compártelo con tu amiga que repite la historia. Comenta PATRÓN 👇
+#mabradiante #relaciones #amorpropio #dependenciaemocional #mty</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>Por qué repites la misma relación #mabradiante #relaciones #amorpropio #dependenciaemocional #mty #shorts</t>
         </is>
       </c>
-      <c r="P5" s="8" t="inlineStr">
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>#mabradiante #relaciones #amorpropio #dependenciaemocional #mty</t>
         </is>
       </c>
-      <c r="Q5" s="8" t="inlineStr">
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R5" s="8" t="inlineStr">
+      <c r="W5" s="8" t="inlineStr">
         <is>
           <t>Romper creencia: "No es que… es que…" (el gancho más repetido en los virales)</t>
         </is>
       </c>
-      <c r="S5" s="8" t="inlineStr">
+      <c r="X5" s="8" t="inlineStr">
         <is>
           <t>Pieza 1 abre el tema del día (rompe una creencia). Mediodía: tus TikToks de 10 a 13 h rinden 1.6x tu mediana (5 videos).</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Y5" s="8" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z5" s="8" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U5" s="7" t="inlineStr"/>
-      <c r="V5" s="7" t="inlineStr"/>
-      <c r="W5" s="7" t="inlineStr"/>
-      <c r="X5" s="7" t="inlineStr"/>
-      <c r="Y5" s="7" t="inlineStr"/>
+      <c r="AA5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB5" s="7" t="inlineStr"/>
+      <c r="AC5" s="7" t="inlineStr"/>
+      <c r="AD5" s="7" t="inlineStr"/>
+      <c r="AE5" s="7" t="inlineStr"/>
+      <c r="AF5" s="7" t="inlineStr"/>
+      <c r="AG5" s="7" t="inlineStr"/>
+      <c r="AH5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="330" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -1342,32 +1597,47 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>MIÉ-2</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Di esto antes de escribirle</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Miércoles 07 · Pieza 2 · Relaciones · apego</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>MIÉ-2</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Relaciones · apego</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>G2 · Promesa práctica</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>Alivio: "algo que puedo hacer ya"</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>[0:00–0:04] GANCHO: "Di esto antes de volver a escribirle a esa persona."
 [0:04–0:13] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con esa amiga que siempre repite la misma historia en el amor."
@@ -1378,67 +1648,99 @@
 [1:05–1:09] CTA: "Sígueme para más hackeos de tu mente y la Matrix."</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>≈ 1:09 min (69 s)</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="N6" s="8" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="O6" s="8" t="inlineStr">
         <is>
           <t>ME ELIJO</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="P6" s="8" t="inlineStr">
         <is>
           <t>Sin venta (conexión)</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="Q6" s="8" t="inlineStr">
         <is>
           <t>Antes de escribirle otra vez, di esto 📵💜 Guárdalo para cuando lo necesites. Comenta ME ELIJO 👇
 #mabradiante #relaciones #amorpropio #dependenciaemocional #mty</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>Antes de escribirle otra vez, di esto 📵💜 Guárdalo para cuando lo necesites. Comenta ME ELIJO 👇
+#mabradiante #relaciones #amorpropio #dependenciaemocional #mty</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>Antes de escribirle otra vez, di esto 📵💜 Guárdalo para cuando lo necesites. Comenta ME ELIJO 👇
+#mabradiante #relaciones #amorpropio #dependenciaemocional #mty</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>Di esto antes de escribirle #mabradiante #relaciones #amorpropio #dependenciaemocional #mty #shorts</t>
         </is>
       </c>
-      <c r="P6" s="8" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>#mabradiante #relaciones #amorpropio #dependenciaemocional #mty</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R6" s="8" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>Algo para usar ya: decreto, respiración o ritual (tu viral de 2.2M y tus 4 más vistos)</t>
         </is>
       </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="X6" s="8" t="inlineStr">
         <is>
           <t>Pieza 2 es la herramienta, la más compartible. Tu mejor horario: de 18 a 21 h tus TikToks rinden 6.3x tu mediana (7 videos).</t>
         </is>
       </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="Y6" s="8" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z6" s="8" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U6" s="7" t="inlineStr"/>
-      <c r="V6" s="7" t="inlineStr"/>
-      <c r="W6" s="7" t="inlineStr"/>
-      <c r="X6" s="7" t="inlineStr"/>
-      <c r="Y6" s="7" t="inlineStr"/>
+      <c r="AA6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB6" s="7" t="inlineStr"/>
+      <c r="AC6" s="7" t="inlineStr"/>
+      <c r="AD6" s="7" t="inlineStr"/>
+      <c r="AE6" s="7" t="inlineStr"/>
+      <c r="AF6" s="7" t="inlineStr"/>
+      <c r="AG6" s="7" t="inlineStr"/>
+      <c r="AH6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="330" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -1456,32 +1758,47 @@
           <t>20:30</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>MIÉ-3</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Deja de esperar a que te elijan</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Miércoles 07 · Pieza 3 · Relaciones · necesitar que te elijan</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>MIÉ-3</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Relaciones · necesitar que te elijan</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>A y B</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>G4 · Pregunta-dolor</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Identificación: "eso me pasa a mí"</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>[0:00–0:05] GANCHO: "Si sigues esperando a que alguien te elija, este video es para ti."
 [0:05–0:14] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con esa amiga que siempre repite la misma historia en el amor."
@@ -1492,67 +1809,99 @@
 [1:00–1:06] CTA: "En Crea y Activa tu Alter Ego te guío paso a paso para instalar esa identidad."</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>≈ 1:06 min (66 s)</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>ALTER EGO</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="P7" s="8" t="inlineStr">
         <is>
           <t>Crea y Activa tu Alter Ego · $599</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="Q7" s="8" t="inlineStr">
         <is>
           <t>Deja de esperar a que te elijan ✨ Guarda este ejercicio de 7 días. Comenta ALTER EGO 👇
 #mabradiante #relaciones #amorpropio #dependenciaemocional #mty</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>Deja de esperar a que te elijan ✨ Guarda este ejercicio de 7 días. Comenta ALTER EGO 👇
+#mabradiante #relaciones #amorpropio #dependenciaemocional #mty</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>Deja de esperar a que te elijan ✨ Guarda este ejercicio de 7 días. Comenta ALTER EGO 👇
+#mabradiante #relaciones #amorpropio #dependenciaemocional #mty</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>Deja de esperar a que te elijan #mabradiante #relaciones #amorpropio #dependenciaemocional #mty #shorts</t>
         </is>
       </c>
-      <c r="P7" s="8" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>#mabradiante #relaciones #amorpropio #dependenciaemocional #mty</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>Pregunta-dolor: nombrar lo que ella siente en sus palabras</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="X7" s="8" t="inlineStr">
         <is>
           <t>Pieza 3 cierra con la venta, cuando ya calentaste el tema con las 2 anteriores. Sigue en tu mejor franja (18 a 21 h).</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="Y7" s="8" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z7" s="8" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="inlineStr"/>
-      <c r="W7" s="7" t="inlineStr"/>
-      <c r="X7" s="7" t="inlineStr"/>
-      <c r="Y7" s="7" t="inlineStr"/>
+      <c r="AA7" s="8" t="inlineStr">
+        <is>
+          <t>Pieza de venta del día (1 de 3).</t>
+        </is>
+      </c>
+      <c r="AB7" s="7" t="inlineStr"/>
+      <c r="AC7" s="7" t="inlineStr"/>
+      <c r="AD7" s="7" t="inlineStr"/>
+      <c r="AE7" s="7" t="inlineStr"/>
+      <c r="AF7" s="7" t="inlineStr"/>
+      <c r="AG7" s="7" t="inlineStr"/>
+      <c r="AH7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="330" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
@@ -1570,32 +1919,47 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>JUE-1</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>No estás perdida: estás despertando</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Jueves 08 · Pieza 1 · Vacío · la vida ya no alcanza</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>JUE-1</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Vacío · la vida ya no alcanza</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>G4 · Pregunta-dolor</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>Identificación: "eso me pasa a mí"</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="L8" s="10" t="inlineStr">
         <is>
           <t>[0:00–0:05] GANCHO: "¿Por qué ya no te hace feliz una vida que antes sí?"
 [0:05–0:12] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien que siente que está despertando."
@@ -1606,67 +1970,99 @@
 [0:53–0:57] CTA: "Sígueme para más hackeos de tu mente y la Matrix."</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>≈ 0:57 min (57 s)</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L8" s="10" t="inlineStr">
+      <c r="O8" s="10" t="inlineStr">
         <is>
           <t>DESPERTANDO</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="P8" s="10" t="inlineStr">
         <is>
           <t>Sin venta (conexión)</t>
         </is>
       </c>
-      <c r="N8" s="10" t="inlineStr">
+      <c r="Q8" s="10" t="inlineStr">
         <is>
           <t>¿Y si no estás perdida… estás despertando? 🌀 Guárdalo y compártelo con quien lo necesita. Comenta DESPERTANDO 👇
 #mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>¿Y si no estás perdida… estás despertando? 🌀 Guárdalo y compártelo con quien lo necesita. Comenta DESPERTANDO 👇
+#mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>¿Y si no estás perdida… estás despertando? 🌀 Guárdalo y compártelo con quien lo necesita. Comenta DESPERTANDO 👇
+#mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty</t>
+        </is>
+      </c>
+      <c r="T8" s="10" t="inlineStr">
         <is>
           <t>No estás perdida: estás despertando #mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty #shorts</t>
         </is>
       </c>
-      <c r="P8" s="10" t="inlineStr">
+      <c r="U8" s="10" t="inlineStr">
         <is>
           <t>#mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="V8" s="10" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R8" s="10" t="inlineStr">
+      <c r="W8" s="10" t="inlineStr">
         <is>
           <t>Pregunta-dolor: nombrar lo que ella siente en sus palabras</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="X8" s="10" t="inlineStr">
         <is>
           <t>Pieza 1 abre el tema del día (rompe una creencia). Mediodía: tus TikToks de 10 a 13 h rinden 1.6x tu mediana (5 videos).</t>
         </is>
       </c>
-      <c r="T8" s="10" t="inlineStr">
+      <c r="Y8" s="10" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z8" s="10" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U8" s="7" t="inlineStr"/>
-      <c r="V8" s="7" t="inlineStr"/>
-      <c r="W8" s="7" t="inlineStr"/>
-      <c r="X8" s="7" t="inlineStr"/>
-      <c r="Y8" s="7" t="inlineStr"/>
+      <c r="AA8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB8" s="7" t="inlineStr"/>
+      <c r="AC8" s="7" t="inlineStr"/>
+      <c r="AD8" s="7" t="inlineStr"/>
+      <c r="AE8" s="7" t="inlineStr"/>
+      <c r="AF8" s="7" t="inlineStr"/>
+      <c r="AG8" s="7" t="inlineStr"/>
+      <c r="AH8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="330" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -1684,32 +2080,47 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>JUE-2</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>200 herramientas y ningún sistema</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Jueves 08 · Pieza 2 · Vacío · información sin sistema (audiencia avanzada)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>JUE-2</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Vacío · información sin sistema (audiencia avanzada)</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>G1 · Reencuadre</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>Sorpresa: "nunca lo había visto así"</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="L9" s="10" t="inlineStr">
         <is>
           <t>[0:00–0:06] GANCHO: "Si sabes de energía, chakras, neuro y biohacking, pero sientes que todo está desconectado, escucha esto."
 [0:06–0:13] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien que siente que está despertando."
@@ -1720,67 +2131,99 @@
 [1:04–1:08] CTA: "Sígueme para más hackeos de tu mente y la Matrix."</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>≈ 1:08 min (68 s)</t>
         </is>
       </c>
-      <c r="K9" s="10" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L9" s="10" t="inlineStr">
+      <c r="O9" s="10" t="inlineStr">
         <is>
           <t>MAPA</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="P9" s="10" t="inlineStr">
         <is>
           <t>Sin venta (conexión)</t>
         </is>
       </c>
-      <c r="N9" s="10" t="inlineStr">
+      <c r="Q9" s="10" t="inlineStr">
         <is>
           <t>Tienes demasiada información y muy poco sistema 🗺️ Guárdalo. Comenta MAPA 👇
 #mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty</t>
         </is>
       </c>
-      <c r="O9" s="10" t="inlineStr">
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>Tienes demasiada información y muy poco sistema 🗺️ Guárdalo. Comenta MAPA 👇
+#mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>Tienes demasiada información y muy poco sistema 🗺️ Guárdalo. Comenta MAPA 👇
+#mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty</t>
+        </is>
+      </c>
+      <c r="T9" s="10" t="inlineStr">
         <is>
           <t>200 herramientas y ningún sistema #mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty #shorts</t>
         </is>
       </c>
-      <c r="P9" s="10" t="inlineStr">
+      <c r="U9" s="10" t="inlineStr">
         <is>
           <t>#mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty</t>
         </is>
       </c>
-      <c r="Q9" s="10" t="inlineStr">
+      <c r="V9" s="10" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R9" s="10" t="inlineStr">
+      <c r="W9" s="10" t="inlineStr">
         <is>
           <t>Romper creencia: "No es que… es que…" (el gancho más repetido en los virales)</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="X9" s="10" t="inlineStr">
         <is>
           <t>Pieza 2 es la herramienta, la más compartible. Tu mejor horario: de 18 a 21 h tus TikToks rinden 6.3x tu mediana (7 videos).</t>
         </is>
       </c>
-      <c r="T9" s="10" t="inlineStr">
+      <c r="Y9" s="10" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z9" s="10" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U9" s="7" t="inlineStr"/>
-      <c r="V9" s="7" t="inlineStr"/>
-      <c r="W9" s="7" t="inlineStr"/>
-      <c r="X9" s="7" t="inlineStr"/>
-      <c r="Y9" s="7" t="inlineStr"/>
+      <c r="AA9" s="10" t="inlineStr">
+        <is>
+          <t>Siembra BNQ™ para la audiencia avanzada, sin vender.</t>
+        </is>
+      </c>
+      <c r="AB9" s="7" t="inlineStr"/>
+      <c r="AC9" s="7" t="inlineStr"/>
+      <c r="AD9" s="7" t="inlineStr"/>
+      <c r="AE9" s="7" t="inlineStr"/>
+      <c r="AF9" s="7" t="inlineStr"/>
+      <c r="AG9" s="7" t="inlineStr"/>
+      <c r="AH9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="330" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
@@ -1798,32 +2241,47 @@
           <t>20:30</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>JUE-3</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>7 señales de que estás despertando</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Jueves 08 · Pieza 3 · Vacío · quiero despertar y no sé cómo</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>JUE-3</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Vacío · quiero despertar y no sé cómo</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>G5 · Espejo/lista</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>Curiosidad: "¿me pasa a mí?"</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="L10" s="10" t="inlineStr">
         <is>
           <t>[0:00–0:05] GANCHO: "La primera señal de un despertar no es sentir paz. Es sentir incomodidad."
 [0:05–0:12] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien que siente que está despertando."
@@ -1834,67 +2292,99 @@
 [0:54–0:57] CTA: "Hice DESPIERTA para darte ese primer mapa."</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>≈ 0:57 min (57 s)</t>
         </is>
       </c>
-      <c r="K10" s="10" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L10" s="10" t="inlineStr">
+      <c r="O10" s="10" t="inlineStr">
         <is>
           <t>DESPIERTA</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="P10" s="10" t="inlineStr">
         <is>
           <t>DESPIERTA · $499</t>
         </is>
       </c>
-      <c r="N10" s="10" t="inlineStr">
+      <c r="Q10" s="10" t="inlineStr">
         <is>
           <t>7 señales de que estás despertando y nadie te lo explicó 🌀 Guarda la lista. Comenta DESPIERTA 👇
 #mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty</t>
         </is>
       </c>
-      <c r="O10" s="10" t="inlineStr">
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>7 señales de que estás despertando y nadie te lo explicó 🌀 Guarda la lista. Comenta DESPIERTA 👇
+#mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>7 señales de que estás despertando y nadie te lo explicó 🌀 Guarda la lista. Comenta DESPIERTA 👇
+#mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty</t>
+        </is>
+      </c>
+      <c r="T10" s="10" t="inlineStr">
         <is>
           <t>7 señales de que estás despertando #mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty #shorts</t>
         </is>
       </c>
-      <c r="P10" s="10" t="inlineStr">
+      <c r="U10" s="10" t="inlineStr">
         <is>
           <t>#mabradiante #despertardeconciencia #espiritualidad #salirdelamatrix #mty</t>
         </is>
       </c>
-      <c r="Q10" s="10" t="inlineStr">
+      <c r="V10" s="10" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R10" s="10" t="inlineStr">
+      <c r="W10" s="10" t="inlineStr">
         <is>
           <t>Lista o espejo: "señales de que…" (formato lista que se guarda)</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="X10" s="10" t="inlineStr">
         <is>
           <t>Pieza 3 cierra con la venta, cuando ya calentaste el tema con las 2 anteriores. Sigue en tu mejor franja (18 a 21 h).</t>
         </is>
       </c>
-      <c r="T10" s="10" t="inlineStr">
+      <c r="Y10" s="10" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 1/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 9/10</t>
+        </is>
+      </c>
+      <c r="Z10" s="10" t="inlineStr">
         <is>
           <t>9/10</t>
         </is>
       </c>
-      <c r="U10" s="7" t="inlineStr"/>
-      <c r="V10" s="7" t="inlineStr"/>
-      <c r="W10" s="7" t="inlineStr"/>
-      <c r="X10" s="7" t="inlineStr"/>
-      <c r="Y10" s="7" t="inlineStr"/>
+      <c r="AA10" s="10" t="inlineStr">
+        <is>
+          <t>Pieza de venta del día (1 de 3). El gancho es tipo lista (G5): vale 1 de 2.</t>
+        </is>
+      </c>
+      <c r="AB10" s="7" t="inlineStr"/>
+      <c r="AC10" s="7" t="inlineStr"/>
+      <c r="AD10" s="7" t="inlineStr"/>
+      <c r="AE10" s="7" t="inlineStr"/>
+      <c r="AF10" s="7" t="inlineStr"/>
+      <c r="AG10" s="7" t="inlineStr"/>
+      <c r="AH10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="330" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -1912,32 +2402,47 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>VIE-1</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>No estás cansada: estás en alerta</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Viernes 09 · Pieza 1 · Cansancio · siempre agotada</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>VIE-1</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>Cansancio · siempre agotada</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>G1 · Reencuadre</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>Sorpresa: "nunca lo había visto así"</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="L11" s="12" t="inlineStr">
         <is>
           <t>[0:00–0:08] GANCHO: "No estás cansada por todo lo que haces. Estás cansada por todo lo que tu cuerpo carga en alerta."
 [0:08–0:17] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien que ya está lista para salir de la Matrix."
@@ -1948,67 +2453,99 @@
 [0:59–1:03] CTA: "Sígueme para más hackeos de tu mente y la Matrix."</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="M11" s="12" t="inlineStr">
         <is>
           <t>≈ 1:03 min (63 s)</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr">
+      <c r="N11" s="12" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L11" s="12" t="inlineStr">
+      <c r="O11" s="12" t="inlineStr">
         <is>
           <t>ENERGÍA</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr">
+      <c r="P11" s="12" t="inlineStr">
         <is>
           <t>Sin venta (conexión)</t>
         </is>
       </c>
-      <c r="N11" s="12" t="inlineStr">
+      <c r="Q11" s="12" t="inlineStr">
         <is>
           <t>No es flojera: es tu cuerpo en alerta 🔋 Guarda este escaneo de 30 segundos. Comenta ENERGÍA 👇
 #mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
         </is>
       </c>
-      <c r="O11" s="12" t="inlineStr">
+      <c r="R11" s="12" t="inlineStr">
+        <is>
+          <t>No es flojera: es tu cuerpo en alerta 🔋 Guarda este escaneo de 30 segundos. Comenta ENERGÍA 👇
+#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
+        </is>
+      </c>
+      <c r="S11" s="12" t="inlineStr">
+        <is>
+          <t>No es flojera: es tu cuerpo en alerta 🔋 Guarda este escaneo de 30 segundos. Comenta ENERGÍA 👇
+#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
+        </is>
+      </c>
+      <c r="T11" s="12" t="inlineStr">
         <is>
           <t>No estás cansada: estás en alerta #mabradiante #hackeatumente #espiritualidad #decreto #mty #shorts</t>
         </is>
       </c>
-      <c r="P11" s="12" t="inlineStr">
+      <c r="U11" s="12" t="inlineStr">
         <is>
           <t>#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
         </is>
       </c>
-      <c r="Q11" s="12" t="inlineStr">
+      <c r="V11" s="12" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R11" s="12" t="inlineStr">
+      <c r="W11" s="12" t="inlineStr">
         <is>
           <t>Romper creencia: "No es que… es que…" (el gancho más repetido en los virales)</t>
         </is>
       </c>
-      <c r="S11" s="12" t="inlineStr">
+      <c r="X11" s="12" t="inlineStr">
         <is>
           <t>Pieza 1 abre el tema del día (rompe una creencia). Mediodía: tus TikToks de 10 a 13 h rinden 1.6x tu mediana (5 videos).</t>
         </is>
       </c>
-      <c r="T11" s="12" t="inlineStr">
+      <c r="Y11" s="12" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z11" s="12" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U11" s="7" t="inlineStr"/>
-      <c r="V11" s="7" t="inlineStr"/>
-      <c r="W11" s="7" t="inlineStr"/>
-      <c r="X11" s="7" t="inlineStr"/>
-      <c r="Y11" s="7" t="inlineStr"/>
+      <c r="AA11" s="12" t="inlineStr">
+        <is>
+          <t>Sin promesas de salud: si el cansancio es fuerte o constante, recomendar ir al médico.</t>
+        </is>
+      </c>
+      <c r="AB11" s="7" t="inlineStr"/>
+      <c r="AC11" s="7" t="inlineStr"/>
+      <c r="AD11" s="7" t="inlineStr"/>
+      <c r="AE11" s="7" t="inlineStr"/>
+      <c r="AF11" s="7" t="inlineStr"/>
+      <c r="AG11" s="7" t="inlineStr"/>
+      <c r="AH11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="330" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -2026,32 +2563,47 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>VIE-2</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Haz esto antes de tocar el celular</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Viernes 09 · Pieza 2 · Energía · arrancar el día en caos</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>VIE-2</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>Energía · arrancar el día en caos</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>G2 · Promesa práctica</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>Alivio: "algo que puedo hacer ya"</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t>[0:00–0:07] GANCHO: "Haz esto al despertar, antes de tocar el celular, y vas a sentir la diferencia en tu energía."
 [0:07–0:14] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien que vive cansada aunque duerma."
@@ -2062,67 +2614,99 @@
 [1:03–1:07] CTA: "Sígueme para más hackeos de tu mente y la Matrix."</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="M12" s="12" t="inlineStr">
         <is>
           <t>≈ 1:07 min (67 s)</t>
         </is>
       </c>
-      <c r="K12" s="12" t="inlineStr">
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L12" s="12" t="inlineStr">
+      <c r="O12" s="12" t="inlineStr">
         <is>
           <t>SOBERANA</t>
         </is>
       </c>
-      <c r="M12" s="12" t="inlineStr">
+      <c r="P12" s="12" t="inlineStr">
         <is>
           <t>Sin venta (conexión)</t>
         </is>
       </c>
-      <c r="N12" s="12" t="inlineStr">
+      <c r="Q12" s="12" t="inlineStr">
         <is>
           <t>El minuto que cambia tu energía antes del celular ☀️ Guárdalo para mañana. Comenta SOBERANA 👇
 #mabradiante #energia #modosupervivencia #ritual #mty</t>
         </is>
       </c>
-      <c r="O12" s="12" t="inlineStr">
+      <c r="R12" s="12" t="inlineStr">
+        <is>
+          <t>El minuto que cambia tu energía antes del celular ☀️ Guárdalo para mañana. Comenta SOBERANA 👇
+#mabradiante #energia #modosupervivencia #ritual #mty</t>
+        </is>
+      </c>
+      <c r="S12" s="12" t="inlineStr">
+        <is>
+          <t>El minuto que cambia tu energía antes del celular ☀️ Guárdalo para mañana. Comenta SOBERANA 👇
+#mabradiante #energia #modosupervivencia #ritual #mty</t>
+        </is>
+      </c>
+      <c r="T12" s="12" t="inlineStr">
         <is>
           <t>Haz esto antes de tocar el celular #mabradiante #energia #modosupervivencia #ritual #mty #shorts</t>
         </is>
       </c>
-      <c r="P12" s="12" t="inlineStr">
+      <c r="U12" s="12" t="inlineStr">
         <is>
           <t>#mabradiante #energia #modosupervivencia #ritual #mty</t>
         </is>
       </c>
-      <c r="Q12" s="12" t="inlineStr">
+      <c r="V12" s="12" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R12" s="12" t="inlineStr">
+      <c r="W12" s="12" t="inlineStr">
         <is>
           <t>Algo para usar ya: decreto, respiración o ritual (tu viral de 2.2M y tus 4 más vistos)</t>
         </is>
       </c>
-      <c r="S12" s="12" t="inlineStr">
+      <c r="X12" s="12" t="inlineStr">
         <is>
           <t>Pieza 2 es la herramienta, la más compartible. Tu mejor horario: de 18 a 21 h tus TikToks rinden 6.3x tu mediana (7 videos).</t>
         </is>
       </c>
-      <c r="T12" s="12" t="inlineStr">
+      <c r="Y12" s="12" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z12" s="12" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U12" s="7" t="inlineStr"/>
-      <c r="V12" s="7" t="inlineStr"/>
-      <c r="W12" s="7" t="inlineStr"/>
-      <c r="X12" s="7" t="inlineStr"/>
-      <c r="Y12" s="7" t="inlineStr"/>
+      <c r="AA12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB12" s="7" t="inlineStr"/>
+      <c r="AC12" s="7" t="inlineStr"/>
+      <c r="AD12" s="7" t="inlineStr"/>
+      <c r="AE12" s="7" t="inlineStr"/>
+      <c r="AF12" s="7" t="inlineStr"/>
+      <c r="AG12" s="7" t="inlineStr"/>
+      <c r="AH12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="330" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -2140,32 +2724,47 @@
           <t>20:30</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>VIE-3</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Señales de que vives en modo supervivencia</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Viernes 09 · Pieza 3 · Estrés · modo supervivencia</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>VIE-3</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>Estrés · modo supervivencia</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>A y B</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>G4 · Pregunta-dolor</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="K13" s="12" t="inlineStr">
         <is>
           <t>Identificación: "eso me pasa a mí"</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>[0:00–0:04] GANCHO: "¿Vives en modo supervivencia y ni siquiera te das cuenta?"
 [0:04–0:13] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien que ya está lista para salir de la Matrix."
@@ -2176,67 +2775,99 @@
 [1:01–1:09] CTA: "En Apaga el Modo Supervivencia tienes el protocolo de biohacking para armonizar tu sistema nervioso y volver al presente."</t>
         </is>
       </c>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="M13" s="12" t="inlineStr">
         <is>
           <t>≈ 1:09 min (69 s)</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr">
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
+      <c r="O13" s="12" t="inlineStr">
         <is>
           <t>VUELVO A MÍ</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr">
+      <c r="P13" s="12" t="inlineStr">
         <is>
           <t>Apaga el Modo Supervivencia · $750</t>
         </is>
       </c>
-      <c r="N13" s="12" t="inlineStr">
+      <c r="Q13" s="12" t="inlineStr">
         <is>
           <t>¿Vives en modo supervivencia? 🧬 Guarda este hackeo de 2 minutos. Comenta VUELVO A MÍ 👇
 #mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
         </is>
       </c>
-      <c r="O13" s="12" t="inlineStr">
+      <c r="R13" s="12" t="inlineStr">
+        <is>
+          <t>¿Vives en modo supervivencia? 🧬 Guarda este hackeo de 2 minutos. Comenta VUELVO A MÍ 👇
+#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
+        </is>
+      </c>
+      <c r="S13" s="12" t="inlineStr">
+        <is>
+          <t>¿Vives en modo supervivencia? 🧬 Guarda este hackeo de 2 minutos. Comenta VUELVO A MÍ 👇
+#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
+        </is>
+      </c>
+      <c r="T13" s="12" t="inlineStr">
         <is>
           <t>Señales de que vives en modo supervivencia #mabradiante #hackeatumente #espiritualidad #decreto #mty #shorts</t>
         </is>
       </c>
-      <c r="P13" s="12" t="inlineStr">
+      <c r="U13" s="12" t="inlineStr">
         <is>
           <t>#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
         </is>
       </c>
-      <c r="Q13" s="12" t="inlineStr">
+      <c r="V13" s="12" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R13" s="12" t="inlineStr">
+      <c r="W13" s="12" t="inlineStr">
         <is>
           <t>Pregunta-dolor: nombrar lo que ella siente en sus palabras</t>
         </is>
       </c>
-      <c r="S13" s="12" t="inlineStr">
+      <c r="X13" s="12" t="inlineStr">
         <is>
           <t>Pieza 3 cierra con la venta, cuando ya calentaste el tema con las 2 anteriores. Sigue en tu mejor franja (18 a 21 h).</t>
         </is>
       </c>
-      <c r="T13" s="12" t="inlineStr">
+      <c r="Y13" s="12" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z13" s="12" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U13" s="7" t="inlineStr"/>
-      <c r="V13" s="7" t="inlineStr"/>
-      <c r="W13" s="7" t="inlineStr"/>
-      <c r="X13" s="7" t="inlineStr"/>
-      <c r="Y13" s="7" t="inlineStr"/>
+      <c r="AA13" s="12" t="inlineStr">
+        <is>
+          <t>Pieza de venta del día (1 de 3). Sin promesas de curación.</t>
+        </is>
+      </c>
+      <c r="AB13" s="7" t="inlineStr"/>
+      <c r="AC13" s="7" t="inlineStr"/>
+      <c r="AD13" s="7" t="inlineStr"/>
+      <c r="AE13" s="7" t="inlineStr"/>
+      <c r="AF13" s="7" t="inlineStr"/>
+      <c r="AG13" s="7" t="inlineStr"/>
+      <c r="AH13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="330" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
@@ -2254,32 +2885,47 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>SÁB-1</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>La meta que siempre dejas para el próximo año</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>Sábado 10 · Pieza 1 · Metas · 'este año sí'</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>SÁB-1</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>Metas · 'este año sí'</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>G4 · Pregunta-dolor</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="K14" s="14" t="inlineStr">
         <is>
           <t>Identificación: "eso me pasa a mí"</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="L14" s="14" t="inlineStr">
         <is>
           <t>[0:00–0:03] GANCHO: "¿Qué meta llevas años diciendo 'este año sí'?"
 [0:03–0:11] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien que lleva años diciendo "este año sí"."
@@ -2290,67 +2936,99 @@
 [1:01–1:05] CTA: "Sígueme para más hackeos de tu mente y la Matrix."</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="M14" s="14" t="inlineStr">
         <is>
           <t>≈ 1:05 min (65 s)</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="N14" s="14" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L14" s="14" t="inlineStr">
+      <c r="O14" s="14" t="inlineStr">
         <is>
           <t>tu meta</t>
         </is>
       </c>
-      <c r="M14" s="14" t="inlineStr">
+      <c r="P14" s="14" t="inlineStr">
         <is>
           <t>Sin venta (conexión)</t>
         </is>
       </c>
-      <c r="N14" s="14" t="inlineStr">
+      <c r="Q14" s="14" t="inlineStr">
         <is>
           <t>¿Qué meta llevas años diciendo 'este año sí'? 🎯 Escríbela en los comentarios: respondo las que más se repitan.
 #mabradiante #metas #leydeatraccion #decreto #mty</t>
         </is>
       </c>
-      <c r="O14" s="14" t="inlineStr">
+      <c r="R14" s="14" t="inlineStr">
+        <is>
+          <t>¿Qué meta llevas años diciendo 'este año sí'? 🎯 Escríbela en los comentarios: respondo las que más se repitan.
+#mabradiante #metas #leydeatraccion #decreto #mty</t>
+        </is>
+      </c>
+      <c r="S14" s="14" t="inlineStr">
+        <is>
+          <t>¿Qué meta llevas años diciendo 'este año sí'? 🎯 Escríbela en los comentarios: respondo las que más se repitan.
+#mabradiante #metas #leydeatraccion #decreto #mty</t>
+        </is>
+      </c>
+      <c r="T14" s="14" t="inlineStr">
         <is>
           <t>La meta que siempre dejas para el próximo año #mabradiante #metas #leydeatraccion #decreto #mty #shorts</t>
         </is>
       </c>
-      <c r="P14" s="14" t="inlineStr">
+      <c r="U14" s="14" t="inlineStr">
         <is>
           <t>#mabradiante #metas #leydeatraccion #decreto #mty</t>
         </is>
       </c>
-      <c r="Q14" s="14" t="inlineStr">
+      <c r="V14" s="14" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R14" s="14" t="inlineStr">
+      <c r="W14" s="14" t="inlineStr">
         <is>
           <t>Pregunta-dolor: nombrar lo que ella siente en sus palabras</t>
         </is>
       </c>
-      <c r="S14" s="14" t="inlineStr">
+      <c r="X14" s="14" t="inlineStr">
         <is>
           <t>Pieza 1 abre el tema del día (rompe una creencia). Mediodía: tus TikToks de 10 a 13 h rinden 1.6x tu mediana (5 videos).</t>
         </is>
       </c>
-      <c r="T14" s="14" t="inlineStr">
+      <c r="Y14" s="14" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 0/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 9/10</t>
+        </is>
+      </c>
+      <c r="Z14" s="14" t="inlineStr">
         <is>
           <t>9/10</t>
         </is>
       </c>
-      <c r="U14" s="7" t="inlineStr"/>
-      <c r="V14" s="7" t="inlineStr"/>
-      <c r="W14" s="7" t="inlineStr"/>
-      <c r="X14" s="7" t="inlineStr"/>
-      <c r="Y14" s="7" t="inlineStr"/>
+      <c r="AA14" s="14" t="inlineStr">
+        <is>
+          <t>Pieza de comunidad: las respuestas te dan ideas de guiones.</t>
+        </is>
+      </c>
+      <c r="AB14" s="7" t="inlineStr"/>
+      <c r="AC14" s="7" t="inlineStr"/>
+      <c r="AD14" s="7" t="inlineStr"/>
+      <c r="AE14" s="7" t="inlineStr"/>
+      <c r="AF14" s="7" t="inlineStr"/>
+      <c r="AG14" s="7" t="inlineStr"/>
+      <c r="AH14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="330" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
@@ -2368,32 +3046,47 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>SÁB-2</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>1 minuto para cambiar tu frecuencia</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>Sábado 10 · Pieza 2 · Comunidad · activación juntas</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>SÁB-2</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>Comunidad · activación juntas</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>G2 · Promesa práctica</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="K15" s="14" t="inlineStr">
         <is>
           <t>Alivio: "algo que puedo hacer ya"</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="L15" s="14" t="inlineStr">
         <is>
           <t>[0:00–0:04] GANCHO: "Hagamos esto juntas ahora: 1 minuto para cambiar tu frecuencia."
 [0:04–0:13] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien que ya está lista para salir de la Matrix."
@@ -2404,67 +3097,99 @@
 [0:56–1:00] CTA: "Sígueme para más hackeos de tu mente y la Matrix."</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="M15" s="14" t="inlineStr">
         <is>
           <t>≈ 1:00 min (60 s)</t>
         </is>
       </c>
-      <c r="K15" s="14" t="inlineStr">
+      <c r="N15" s="14" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L15" s="14" t="inlineStr">
+      <c r="O15" s="14" t="inlineStr">
         <is>
           <t>COHERENCIA</t>
         </is>
       </c>
-      <c r="M15" s="14" t="inlineStr">
+      <c r="P15" s="14" t="inlineStr">
         <is>
           <t>Sin venta (conexión)</t>
         </is>
       </c>
-      <c r="N15" s="14" t="inlineStr">
+      <c r="Q15" s="14" t="inlineStr">
         <is>
           <t>1 minuto de coherencia, juntas 💛 Guárdalo y compártelo. Comenta COHERENCIA 👇
 #mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
         </is>
       </c>
-      <c r="O15" s="14" t="inlineStr">
+      <c r="R15" s="14" t="inlineStr">
+        <is>
+          <t>1 minuto de coherencia, juntas 💛 Guárdalo y compártelo. Comenta COHERENCIA 👇
+#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
+        </is>
+      </c>
+      <c r="S15" s="14" t="inlineStr">
+        <is>
+          <t>1 minuto de coherencia, juntas 💛 Guárdalo y compártelo. Comenta COHERENCIA 👇
+#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
+        </is>
+      </c>
+      <c r="T15" s="14" t="inlineStr">
         <is>
           <t>1 minuto para cambiar tu frecuencia #mabradiante #hackeatumente #espiritualidad #decreto #mty #shorts</t>
         </is>
       </c>
-      <c r="P15" s="14" t="inlineStr">
+      <c r="U15" s="14" t="inlineStr">
         <is>
           <t>#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
         </is>
       </c>
-      <c r="Q15" s="14" t="inlineStr">
+      <c r="V15" s="14" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R15" s="14" t="inlineStr">
+      <c r="W15" s="14" t="inlineStr">
         <is>
           <t>Algo para usar ya: decreto, respiración o ritual (tu viral de 2.2M y tus 4 más vistos)</t>
         </is>
       </c>
-      <c r="S15" s="14" t="inlineStr">
+      <c r="X15" s="14" t="inlineStr">
         <is>
           <t>Pieza 2 es la herramienta, la más compartible. Tu mejor horario: de 18 a 21 h tus TikToks rinden 6.3x tu mediana (7 videos).</t>
         </is>
       </c>
-      <c r="T15" s="14" t="inlineStr">
+      <c r="Y15" s="14" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z15" s="14" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U15" s="7" t="inlineStr"/>
-      <c r="V15" s="7" t="inlineStr"/>
-      <c r="W15" s="7" t="inlineStr"/>
-      <c r="X15" s="7" t="inlineStr"/>
-      <c r="Y15" s="7" t="inlineStr"/>
+      <c r="AA15" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB15" s="7" t="inlineStr"/>
+      <c r="AC15" s="7" t="inlineStr"/>
+      <c r="AD15" s="7" t="inlineStr"/>
+      <c r="AE15" s="7" t="inlineStr"/>
+      <c r="AF15" s="7" t="inlineStr"/>
+      <c r="AG15" s="7" t="inlineStr"/>
+      <c r="AH15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="330" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
@@ -2482,32 +3207,47 @@
           <t>20:30</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>SÁB-3</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>La creencia que no sabes que tienes</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>Sábado 10 · Pieza 3 · Metas · creencias limitantes</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>SÁB-3</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>Metas · creencias limitantes</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>A y B</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>G1 · Creencia rota</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="K16" s="14" t="inlineStr">
         <is>
           <t>Sorpresa: "nunca lo había visto así"</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="L16" s="14" t="inlineStr">
         <is>
           <t>[0:00–0:04] GANCHO: "La creencia más peligrosa es la que no sabes que tienes."
 [0:04–0:12] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien que lleva años diciendo "este año sí"."
@@ -2518,67 +3258,99 @@
 [0:58–1:06] CTA: "Si quieres hackear la creencia que no te deja avanzar, comenta NIVEL 1 y te mando el link de DESPERTAR."</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="M16" s="14" t="inlineStr">
         <is>
           <t>≈ 1:06 min (66 s)</t>
         </is>
       </c>
-      <c r="K16" s="14" t="inlineStr">
+      <c r="N16" s="14" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L16" s="14" t="inlineStr">
+      <c r="O16" s="14" t="inlineStr">
         <is>
           <t>NIVEL 1</t>
         </is>
       </c>
-      <c r="M16" s="14" t="inlineStr">
+      <c r="P16" s="14" t="inlineStr">
         <is>
           <t>Nivel 1 DESPERTAR · $2,000</t>
         </is>
       </c>
-      <c r="N16" s="14" t="inlineStr">
+      <c r="Q16" s="14" t="inlineStr">
         <is>
           <t>La creencia más peligrosa es la que no sabes que tienes 🔓 Haz el ejercicio. Comenta NIVEL 1 👇
 #mabradiante #metas #leydeatraccion #decreto #mty</t>
         </is>
       </c>
-      <c r="O16" s="14" t="inlineStr">
+      <c r="R16" s="14" t="inlineStr">
+        <is>
+          <t>La creencia más peligrosa es la que no sabes que tienes 🔓 Haz el ejercicio. Comenta NIVEL 1 👇
+#mabradiante #metas #leydeatraccion #decreto #mty</t>
+        </is>
+      </c>
+      <c r="S16" s="14" t="inlineStr">
+        <is>
+          <t>La creencia más peligrosa es la que no sabes que tienes 🔓 Haz el ejercicio. Comenta NIVEL 1 👇
+#mabradiante #metas #leydeatraccion #decreto #mty</t>
+        </is>
+      </c>
+      <c r="T16" s="14" t="inlineStr">
         <is>
           <t>La creencia que no sabes que tienes #mabradiante #metas #leydeatraccion #decreto #mty #shorts</t>
         </is>
       </c>
-      <c r="P16" s="14" t="inlineStr">
+      <c r="U16" s="14" t="inlineStr">
         <is>
           <t>#mabradiante #metas #leydeatraccion #decreto #mty</t>
         </is>
       </c>
-      <c r="Q16" s="14" t="inlineStr">
+      <c r="V16" s="14" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R16" s="14" t="inlineStr">
+      <c r="W16" s="14" t="inlineStr">
         <is>
           <t>Romper creencia: "No es que… es que…" (el gancho más repetido en los virales)</t>
         </is>
       </c>
-      <c r="S16" s="14" t="inlineStr">
+      <c r="X16" s="14" t="inlineStr">
         <is>
           <t>Pieza 3 cierra con la venta, cuando ya calentaste el tema con las 2 anteriores. Sigue en tu mejor franja (18 a 21 h).</t>
         </is>
       </c>
-      <c r="T16" s="14" t="inlineStr">
+      <c r="Y16" s="14" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z16" s="14" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U16" s="7" t="inlineStr"/>
-      <c r="V16" s="7" t="inlineStr"/>
-      <c r="W16" s="7" t="inlineStr"/>
-      <c r="X16" s="7" t="inlineStr"/>
-      <c r="Y16" s="7" t="inlineStr"/>
+      <c r="AA16" s="14" t="inlineStr">
+        <is>
+          <t>Pieza de venta del día (1 de 3). Vende el Nivel 1, que ya está completo.</t>
+        </is>
+      </c>
+      <c r="AB16" s="7" t="inlineStr"/>
+      <c r="AC16" s="7" t="inlineStr"/>
+      <c r="AD16" s="7" t="inlineStr"/>
+      <c r="AE16" s="7" t="inlineStr"/>
+      <c r="AF16" s="7" t="inlineStr"/>
+      <c r="AG16" s="7" t="inlineStr"/>
+      <c r="AH16" s="7" t="inlineStr"/>
     </row>
     <row r="17" ht="330" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
@@ -2596,32 +3368,47 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>DOM-1</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>Detecta tu programa en 2 minutos</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>Domingo 11 · Pieza 1 · Patrones · el programa que se repite</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>DOM-1</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>Patrones · el programa que se repite</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>G3 · Técnica paso a paso</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="K17" s="16" t="inlineStr">
         <is>
           <t>s/d</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="L17" s="16" t="inlineStr">
         <is>
           <t>[0:00–0:07] GANCHO: "Hoy te enseño a detectar en 2 minutos el programa que más se repite en tu vida."
 [0:07–0:16] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien que ya está lista para salir de la Matrix."
@@ -2632,67 +3419,99 @@
 [0:54–0:58] CTA: "Sígueme para más hackeos de tu mente y la Matrix."</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="M17" s="16" t="inlineStr">
         <is>
           <t>≈ 0:58 min (58 s)</t>
         </is>
       </c>
-      <c r="K17" s="16" t="inlineStr">
+      <c r="N17" s="16" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L17" s="16" t="inlineStr">
+      <c r="O17" s="16" t="inlineStr">
         <is>
           <t>PROGRAMA</t>
         </is>
       </c>
-      <c r="M17" s="16" t="inlineStr">
+      <c r="P17" s="16" t="inlineStr">
         <is>
           <t>Sin venta (conexión)</t>
         </is>
       </c>
-      <c r="N17" s="16" t="inlineStr">
+      <c r="Q17" s="16" t="inlineStr">
         <is>
           <t>Detecta en 2 minutos el programa que más se repite en tu vida 🧩 Guárdalo. Comenta PROGRAMA 👇
 #mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
         </is>
       </c>
-      <c r="O17" s="16" t="inlineStr">
+      <c r="R17" s="16" t="inlineStr">
+        <is>
+          <t>Detecta en 2 minutos el programa que más se repite en tu vida 🧩 Guárdalo. Comenta PROGRAMA 👇
+#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
+        </is>
+      </c>
+      <c r="S17" s="16" t="inlineStr">
+        <is>
+          <t>Detecta en 2 minutos el programa que más se repite en tu vida 🧩 Guárdalo. Comenta PROGRAMA 👇
+#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
+        </is>
+      </c>
+      <c r="T17" s="16" t="inlineStr">
         <is>
           <t>Detecta tu programa en 2 minutos #mabradiante #hackeatumente #espiritualidad #decreto #mty #shorts</t>
         </is>
       </c>
-      <c r="P17" s="16" t="inlineStr">
+      <c r="U17" s="16" t="inlineStr">
         <is>
           <t>#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
         </is>
       </c>
-      <c r="Q17" s="16" t="inlineStr">
+      <c r="V17" s="16" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R17" s="16" t="inlineStr">
+      <c r="W17" s="16" t="inlineStr">
         <is>
           <t>G3 · Técnica paso a paso</t>
         </is>
       </c>
-      <c r="S17" s="16" t="inlineStr">
+      <c r="X17" s="16" t="inlineStr">
         <is>
           <t>Pieza 1 abre el tema del día (rompe una creencia). Mediodía: tus TikToks de 10 a 13 h rinden 1.6x tu mediana (5 videos).</t>
         </is>
       </c>
-      <c r="T17" s="16" t="inlineStr">
+      <c r="Y17" s="16" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z17" s="16" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U17" s="7" t="inlineStr"/>
-      <c r="V17" s="7" t="inlineStr"/>
-      <c r="W17" s="7" t="inlineStr"/>
-      <c r="X17" s="7" t="inlineStr"/>
-      <c r="Y17" s="7" t="inlineStr"/>
+      <c r="AA17" s="16" t="inlineStr">
+        <is>
+          <t>Sin venta.</t>
+        </is>
+      </c>
+      <c r="AB17" s="7" t="inlineStr"/>
+      <c r="AC17" s="7" t="inlineStr"/>
+      <c r="AD17" s="7" t="inlineStr"/>
+      <c r="AE17" s="7" t="inlineStr"/>
+      <c r="AF17" s="7" t="inlineStr"/>
+      <c r="AG17" s="7" t="inlineStr"/>
+      <c r="AH17" s="7" t="inlineStr"/>
     </row>
     <row r="18" ht="330" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
@@ -2710,32 +3529,47 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>DOM-2</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>Espiritualidad y ciencia no son lo mismo</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Domingo 11 · Pieza 2 · Posicionamiento · espiritualidad vs ciencia</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>DOM-2</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>Posicionamiento · espiritualidad vs ciencia</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>G1 · Frase polémica</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="K18" s="16" t="inlineStr">
         <is>
           <t>Sorpresa: "nunca lo había visto así"</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="L18" s="16" t="inlineStr">
         <is>
           <t>[0:00–0:06] GANCHO: "No quiero convencerte de que la espiritualidad es ciencia. Quiero que aprendas a distinguirlas."
 [0:06–0:15] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien que ya está lista para salir de la Matrix."
@@ -2746,67 +3580,99 @@
 [0:57–1:01] CTA: "Sígueme para más hackeos de tu mente y la Matrix."</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="M18" s="16" t="inlineStr">
         <is>
           <t>≈ 1:01 min (61 s)</t>
         </is>
       </c>
-      <c r="K18" s="16" t="inlineStr">
+      <c r="N18" s="16" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L18" s="16" t="inlineStr">
+      <c r="O18" s="16" t="inlineStr">
         <is>
           <t>MAPAS</t>
         </is>
       </c>
-      <c r="M18" s="16" t="inlineStr">
+      <c r="P18" s="16" t="inlineStr">
         <is>
           <t>Sin venta (conexión)</t>
         </is>
       </c>
-      <c r="N18" s="16" t="inlineStr">
+      <c r="Q18" s="16" t="inlineStr">
         <is>
           <t>No quiero convencerte de que la espiritualidad es ciencia ⚖️ Guárdalo y compártelo. Comenta MAPAS 👇
 #mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
         </is>
       </c>
-      <c r="O18" s="16" t="inlineStr">
+      <c r="R18" s="16" t="inlineStr">
+        <is>
+          <t>No quiero convencerte de que la espiritualidad es ciencia ⚖️ Guárdalo y compártelo. Comenta MAPAS 👇
+#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
+        </is>
+      </c>
+      <c r="S18" s="16" t="inlineStr">
+        <is>
+          <t>No quiero convencerte de que la espiritualidad es ciencia ⚖️ Guárdalo y compártelo. Comenta MAPAS 👇
+#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
+        </is>
+      </c>
+      <c r="T18" s="16" t="inlineStr">
         <is>
           <t>Espiritualidad y ciencia no son lo mismo #mabradiante #hackeatumente #espiritualidad #decreto #mty #shorts</t>
         </is>
       </c>
-      <c r="P18" s="16" t="inlineStr">
+      <c r="U18" s="16" t="inlineStr">
         <is>
           <t>#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
         </is>
       </c>
-      <c r="Q18" s="16" t="inlineStr">
+      <c r="V18" s="16" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R18" s="16" t="inlineStr">
+      <c r="W18" s="16" t="inlineStr">
         <is>
           <t>Romper creencia: "No es que… es que…" (el gancho más repetido en los virales)</t>
         </is>
       </c>
-      <c r="S18" s="16" t="inlineStr">
+      <c r="X18" s="16" t="inlineStr">
         <is>
           <t>Pieza 2 es la herramienta, la más compartible. Tu mejor horario: de 18 a 21 h tus TikToks rinden 6.3x tu mediana (7 videos).</t>
         </is>
       </c>
-      <c r="T18" s="16" t="inlineStr">
+      <c r="Y18" s="16" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 1/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 9/10</t>
+        </is>
+      </c>
+      <c r="Z18" s="16" t="inlineStr">
         <is>
           <t>9/10</t>
         </is>
       </c>
-      <c r="U18" s="7" t="inlineStr"/>
-      <c r="V18" s="7" t="inlineStr"/>
-      <c r="W18" s="7" t="inlineStr"/>
-      <c r="X18" s="7" t="inlineStr"/>
-      <c r="Y18" s="7" t="inlineStr"/>
+      <c r="AA18" s="16" t="inlineStr">
+        <is>
+          <t>Sin venta. Posiciona a Mabel con la audiencia avanzada. La microherramienta es una pregunta: vale 1 de 2.</t>
+        </is>
+      </c>
+      <c r="AB18" s="7" t="inlineStr"/>
+      <c r="AC18" s="7" t="inlineStr"/>
+      <c r="AD18" s="7" t="inlineStr"/>
+      <c r="AE18" s="7" t="inlineStr"/>
+      <c r="AF18" s="7" t="inlineStr"/>
+      <c r="AG18" s="7" t="inlineStr"/>
+      <c r="AH18" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="330" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
@@ -2824,32 +3690,47 @@
           <t>20:30</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>DOM-3</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>Decreto de domingo para tu semana</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>Domingo 11 · Pieza 3 · Semana nueva · decreto</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>TikTok · Instagram Reels · Facebook Reels · YouTube Shorts</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>DOM-3</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>Semana nueva · decreto</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>G2 · Promesa práctica</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="K19" s="16" t="inlineStr">
         <is>
           <t>Alivio: "algo que puedo hacer ya"</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="L19" s="16" t="inlineStr">
         <is>
           <t>[0:00–0:06] GANCHO: "Di esto el domingo en la noche y empieza tu semana en otra frecuencia."
 [0:06–0:15] GUARDAR Y COMPARTIR: "Guarda este video antes de que se te pierda y compártelo con alguien que ya está lista para salir de la Matrix."
@@ -2860,94 +3741,126 @@
 [0:57–1:01] CTA: "Sígueme para más hackeos de tu mente y la Matrix."</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="M19" s="16" t="inlineStr">
         <is>
           <t>≈ 1:01 min (61 s)</t>
         </is>
       </c>
-      <c r="K19" s="16" t="inlineStr">
+      <c r="N19" s="16" t="inlineStr">
         <is>
           <t>Video vertical 9:16, cara a cámara. El mismo video va a las 4 redes.</t>
         </is>
       </c>
-      <c r="L19" s="16" t="inlineStr">
+      <c r="O19" s="16" t="inlineStr">
         <is>
           <t>HECHO ESTÁ</t>
         </is>
       </c>
-      <c r="M19" s="16" t="inlineStr">
+      <c r="P19" s="16" t="inlineStr">
         <is>
           <t>Sin venta (conexión)</t>
         </is>
       </c>
-      <c r="N19" s="16" t="inlineStr">
+      <c r="Q19" s="16" t="inlineStr">
         <is>
           <t>Di esto el domingo en la noche 🌙 Guárdalo para cada semana. Comenta HECHO ESTÁ 👇
 #mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
         </is>
       </c>
-      <c r="O19" s="16" t="inlineStr">
+      <c r="R19" s="16" t="inlineStr">
+        <is>
+          <t>Di esto el domingo en la noche 🌙 Guárdalo para cada semana. Comenta HECHO ESTÁ 👇
+#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
+        </is>
+      </c>
+      <c r="S19" s="16" t="inlineStr">
+        <is>
+          <t>Di esto el domingo en la noche 🌙 Guárdalo para cada semana. Comenta HECHO ESTÁ 👇
+#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
+        </is>
+      </c>
+      <c r="T19" s="16" t="inlineStr">
         <is>
           <t>Decreto de domingo para tu semana #mabradiante #hackeatumente #espiritualidad #decreto #mty #shorts</t>
         </is>
       </c>
-      <c r="P19" s="16" t="inlineStr">
+      <c r="U19" s="16" t="inlineStr">
         <is>
           <t>#mabradiante #hackeatumente #espiritualidad #decreto #mty</t>
         </is>
       </c>
-      <c r="Q19" s="16" t="inlineStr">
+      <c r="V19" s="16" t="inlineStr">
         <is>
           <t>Meta: superar tu mediana de TikTok (11,850 vistas). Viral para ti: más de 17,775 (1.5x). Instagram, Facebook y YouTube: s/d, los medimos en la rutina semanal.</t>
         </is>
       </c>
-      <c r="R19" s="16" t="inlineStr">
+      <c r="W19" s="16" t="inlineStr">
         <is>
           <t>Algo para usar ya: decreto, respiración o ritual (tu viral de 2.2M y tus 4 más vistos)</t>
         </is>
       </c>
-      <c r="S19" s="16" t="inlineStr">
+      <c r="X19" s="16" t="inlineStr">
         <is>
           <t>Pieza 3 cierra con la venta, cuando ya calentaste el tema con las 2 anteriores. Sigue en tu mejor franja (18 a 21 h).</t>
         </is>
       </c>
-      <c r="T19" s="16" t="inlineStr">
+      <c r="Y19" s="16" t="inlineStr">
+        <is>
+          <t>Primera frase = gancho G1 a G4: 2/2
+Quita la culpa antes de enseñar: 1/1
+Un dato de ciencia simple: 1/1
+Algo para usar ya: 2/2
+Pide guardar/compartir en 15 s: 1/1
+Pide comentar una palabra: 1/1
+Venta al final en 1 frase (o sin venta): 1/1
+Vocabulario BNQ™, nada prohibido: 1/1
+Total: 10/10</t>
+        </is>
+      </c>
+      <c r="Z19" s="16" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="U19" s="7" t="inlineStr"/>
-      <c r="V19" s="7" t="inlineStr"/>
-      <c r="W19" s="7" t="inlineStr"/>
-      <c r="X19" s="7" t="inlineStr"/>
-      <c r="Y19" s="7" t="inlineStr"/>
+      <c r="AA19" s="16" t="inlineStr">
+        <is>
+          <t>Sin venta. Mismo formato que tu video viral de 2.2M.</t>
+        </is>
+      </c>
+      <c r="AB19" s="7" t="inlineStr"/>
+      <c r="AC19" s="7" t="inlineStr"/>
+      <c r="AD19" s="7" t="inlineStr"/>
+      <c r="AE19" s="7" t="inlineStr"/>
+      <c r="AF19" s="7" t="inlineStr"/>
+      <c r="AG19" s="7" t="inlineStr"/>
+      <c r="AH19" s="7" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="T21" s="18" t="inlineStr">
+      <c r="AA21" s="18" t="inlineStr">
         <is>
           <t>Grabadas:</t>
         </is>
       </c>
-      <c r="U21" s="18">
-        <f>COUNTIF(U2:U19,"Sí")&amp;" de "&amp;COUNTA(E2:E19)</f>
+      <c r="AB21" s="18">
+        <f>COUNTIF(AB2:AB19,"Sí")&amp;" de "&amp;COUNTA(D2:D19)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="T22" s="18" t="inlineStr">
+      <c r="AA22" s="18" t="inlineStr">
         <is>
           <t>Publicadas:</t>
         </is>
       </c>
-      <c r="U22" s="18">
-        <f>COUNTIF(V2:V19,"Sí")&amp;" de "&amp;COUNTA(E2:E19)</f>
+      <c r="AB22" s="18">
+        <f>COUNTIF(AC2:AC19,"Sí")&amp;" de "&amp;COUNTA(D2:D19)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y19"/>
+  <autoFilter ref="A1:AH19"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2:V19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AB2:AC19 AH2:AH19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2956,6 +3869,1020 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>PIEZA</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>TÍTULO DEL VIDEO</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>HOOK (primera frase, sin saludar)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>GUARDA (antes del segundo 15)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>PROBLEMA Y SÍNTOMA</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>REENCUADRE</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>PUENTE ESPIRITUAL + CIENTÍFICO</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>MICROHERRAMIENTA (para hacer ya)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>REVELACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>MAR-1</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>No era ansiedad: era una mente sin dirección</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Durante años creí que tenía ansiedad. Lo que tenía era una mente que nadie me enseñó a dirigir.</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Te acuestas y tu cabeza empieza a repasar todo: lo que dijiste, lo que falta, lo que podría salir mal.</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>No estás rota. Tu mente está haciendo su trabajo: protegerte. Yo vivo con TDAH y aprendí que mi mente no necesitaba callarse; necesitaba dirección.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>En las tradiciones contemplativas a esto se le llama 'la mente de mono'. La psicología le llama rumiación: el cerebro repite lo que siente sin resolver.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Esta noche escribe en un papel TODO lo que tu mente está cargando. Al final escribe: 'Por hoy, esto ya está fuera de mí.'</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Tu mente no se calma cuando la obligas. Se calma cuando siente que ya no tiene que cargarlo todo sola.</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Comenta MENTE y te mando el siguiente hackeo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>MAR-2</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Respiración de 60 segundos para la ansiedad</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Haz esto 60 segundos cuando sientas que la ansiedad te sube al pecho.</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>El corazón se acelera, la respiración se corta y sientes que algo malo va a pasar aunque no esté pasando nada.</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>No es debilidad: es tu sistema nervioso en modo alarma.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>La ciencia: exhalar más largo de lo que inhalas activa el sistema nervioso parasimpático, el freno natural de tu cuerpo. En mi marco BNQ™ a esto le llamo recuperar tu soberanía energética.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Mano en el pecho. Inhala en 4… exhala en 8. Seis veces, conmigo.</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>No tienes que convencer a tu mente de que se calme. Le muestras a tu cuerpo que está a salvo y la mente lo sigue.</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Guárdalo para cuando lo necesites y comenta CALMA si lo hiciste conmigo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MAR-3</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Por qué tu mente se acelera al dormir</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>¿Por qué tu mente se acelera justo cuando por fin te acuestas a dormir?</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Todo el día corres, y en la noche, cuando todo se apaga, tu mente se prende.</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>No es que no sepas descansar. Es que tu sistema nervioso aprendió que bajar la guardia es peligroso.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>La ciencia: cuando vives en estrés constante, tu cuerpo se queda en alerta y el sueño profundo cuesta más. Desde lo energético: es una mente que nunca cerró su día.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Antes de dormir di tres veces, despacio: 'Hoy ya terminó. Mi cuerpo está a salvo.'</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>El descanso no llega cuando apagas la luz. Llega cuando tu sistema entiende que ya puede soltar.</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Si tu mente no te deja dormir, en Querida Ansiedad te doy la auditoría mental y los audios para bajar su velocidad. Comenta DORMIR y te mando el link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>MIÉ-1</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Por qué repites la misma relación</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>No es que siempre te toque la persona equivocada. Es que tu sistema reconoce como 'amor' lo que ya conoce.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Cambias de pareja, pero la historia se repite: das de más, esperas, te decepcionas.</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>No eres tú la que está mal. Aprendiste en casa cómo se sentía el amor, y tu sistema busca lo familiar aunque duela.</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>La psicología lo explica con los estilos de apego que se forman en la infancia. En lo espiritual se habla de patrones que llegan para mostrarte lo que falta sanar.</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Escribe las 3 cosas que se repiten en TODAS tus relaciones. Ese es tu patrón, no tu destino.</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>No necesitas encontrar a otra persona. Necesitas dejar de buscar con el mismo programa.</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Comenta PATRÓN y te mando la parte 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>MIÉ-2</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Di esto antes de escribirle</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Di esto antes de volver a escribirle a esa persona.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Tienes el celular en la mano, sabes que no deberías, y aun así lo vas a hacer.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>No es falta de dignidad. Es tu sistema buscando alivio en lo conocido.</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>La ciencia: la incertidumbre de si te va a contestar engancha tu sistema de recompensa, por eso es tan difícil soltar el celular. En lo energético: es tu energía saliendo hacia afuera.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Pon el celular boca abajo, respira tres veces y di: 'Me elijo a mí primero. Lo que es para mí no lo tengo que perseguir.'</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Cada vez que no escribes desde la ansiedad, le enseñas a tu cuerpo una forma nueva de amor.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Guárdalo para la próxima vez y comenta ME ELIJO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>MIÉ-3</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Deja de esperar a que te elijan</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Si sigues esperando a que alguien te elija, este video es para ti.</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Revisas si vio tu historia, si te contestó, si sigue en línea.</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>No te falta el amor de otros. Te falta una identidad que no dependa de ellos.</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>La neuroplasticidad nos dice que el cerebro aprende nuevas formas de verse a sí mismo con práctica repetida. En lo espiritual, es recordar quién eres.</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Escribe cómo pensaría, hablaría y elegiría la versión de ti que ya se siente suficiente. Léelo cada mañana durante 7 días.</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Cuando cambias quién eres por dentro, cambias a quién atraes y a quién dejas ir.</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>En Crea y Activa tu Alter Ego te guío paso a paso para instalar esa identidad. Comenta ALTER EGO y te mando el link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>JUE-1</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>No estás perdida: estás despertando</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>¿Por qué ya no te hace feliz una vida que antes sí?</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Te levantas, trabajas, cumples, resuelves… y por dentro sientes que algo no encaja.</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Quizá no estás perdida. Quizá estás despertando.</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>En espiritualidad lo llamamos despertar de consciencia. Desde la psicología también puede ser una revisión profunda de tu identidad, tus valores y tus patrones aprendidos.</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Hazte hoy una sola pregunta: ¿qué parte de mi vida sigo sosteniendo solo porque siempre ha sido así?</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>La incomodidad no es el problema. Es la señal de que ya no cabes en la vida que construiste en automático.</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Si te pasa, comenta DESPERTANDO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>JUE-2</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>200 herramientas y ningún sistema</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Si sabes de energía, chakras, neuro y biohacking, pero sientes que todo está desconectado, escucha esto.</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Un maestro te habla del cuerpo, otro del subconsciente, otro de la energía… y terminas con 200 herramientas y ningún sistema.</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>No necesitas otra herramienta. Necesitas un mapa.</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Mi trabajo no es hacerte elegir entre espiritualidad y ciencia: es distinguir los mapas y construir el puente. La neurociencia muestra que el cerebro cambia con la repetición, no con la cantidad de información.</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Haz una lista de todas las prácticas que conoces y marca solo las que haces de verdad cada semana. Esa diferencia es tu punto de partida.</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>La transformación no está en saber más. Está en tener un orden.</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Comenta MAPA y te cuento cómo ordeno todo en mi sistema BNQ™.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>JUE-3</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>7 señales de que estás despertando</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>La primera señal de un despertar no es sentir paz. Es sentir incomodidad.</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Cuestionas lo que antes aceptabas, necesitas estar más sola, ciertas personas ya no te representan, buscas significado, empiezas a ver tus patrones, tienes preguntas nuevas y sientes que hay algo más.</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Si te identificas con varias, no te estás volviendo rara: estás despertando.</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>En lo espiritual es despertar. En psicología, una etapa de revisión de identidad.</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Guarda esta lista y marca cuántas vives hoy.</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>No necesitas consumir 200 videos más para entender qué te pasa. Necesitas un primer mapa.</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Hice DESPIERTA para darte ese primer mapa. Comenta DESPIERTA y te mando el link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>VIE-1</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>No estás cansada: estás en alerta</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>No estás cansada por todo lo que haces. Estás cansada por todo lo que tu cuerpo carga en alerta.</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Duermes y despiertas cansada. Cuello tenso, mandíbula apretada, hombros arriba.</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>No es flojera. Es un sistema nervioso que no ha tenido permiso de descansar.</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>La ciencia: el estrés crónico mantiene activa la respuesta de lucha o huida, y eso agota. En lo energético: es energía que se fuga en sostenerlo todo.</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>Ahora mismo: afloja la mandíbula, baja los hombros y exhala largo 3 veces. Repítelo 3 veces al día.</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>Tu energía no se recupera solo durmiendo. Se recupera cuando tu cuerpo deja de defenderse.</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>Comenta ENERGÍA si te pasa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>VIE-2</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Haz esto antes de tocar el celular</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Haz esto al despertar, antes de tocar el celular, y vas a sentir la diferencia en tu energía.</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Abres los ojos, agarras el celular y en un minuto ya estás respondiendo a todos menos a ti.</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>No es que te falte disciplina. Es que le entregas tu energía al mundo antes de dártela a ti.</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>La ciencia: revisar el celular apenas despiertas pone a tu cerebro en modo reacción desde el primer minuto. En mi marco BNQ™: es empezar el día sin soberanía energética.</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>1 minuto: pies en el piso, mano en el corazón, 5 respiraciones lentas y una intención: 'Hoy mi energía es mía.'</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>Como empiezas tu mañana es como le enseñas a tu sistema quién manda.</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>Guárdalo y comenta SOBERANA si lo haces mañana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>VIE-3</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Señales de que vives en modo supervivencia</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>¿Vives en modo supervivencia y ni siquiera te das cuenta?</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Todo te sobresalta, no puedes estar sin hacer nada y te enfermas justo cuando por fin descansas.</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Tu cuerpo no te está fallando: te está protegiendo de más.</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Biohacking es usar respiración, descanso y hábitos para hablarle a tu sistema nervioso en su idioma. La ciencia muestra que la respiración lenta ayuda a bajar la respuesta de estrés.</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>Hoy pon una alarma a media tarde y haz 2 minutos de respiración lenta, sin celular.</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>Salir del modo supervivencia no es hacer menos: es enseñarle a tu cuerpo que ya está a salvo.</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>En Apaga el Modo Supervivencia tienes el protocolo de biohacking para armonizar tu sistema nervioso y volver al presente. Comenta VUELVO A MÍ y te mando el link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>SÁB-1</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>La meta que siempre dejas para el próximo año</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>¿Qué meta llevas años diciendo 'este año sí'?</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>En enero empiezas con todo, en marzo ya lo dejaste, y en diciembre te prometes lo mismo.</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>No es falta de disciplina. Es una creencia que dice 'eso no es para mí'.</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>La psicología le llama autosabotaje: tu mente protege lo conocido, aunque no te guste. En lo espiritual: un programa que todavía no has visto.</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Escribe tu meta y, debajo, la primera frase que aparece cuando la imaginas cumplida. Esa frase es el programa.</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>La meta no se te escapa: la frena una versión de ti que todavía no cree que la merece.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Comenta tu meta: este fin de semana respondo en video las que más se repitan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>SÁB-2</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>1 minuto para cambiar tu frecuencia</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Hagamos esto juntas ahora: 1 minuto para cambiar tu frecuencia.</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Fin de semana, cansancio acumulado, la cabeza en mil cosas.</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>No necesitas una hora de meditación. Necesitas un minuto de coherencia.</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>La ciencia: respirar a un ritmo lento y parejo ayuda a regular tu ritmo cardiaco (coherencia cardiaca). Es la base de mi Fórmula F·01, Coherencia Energética Integral (CEI™).</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>Mano en el corazón. Inhala en 5… exhala en 5. Seis veces conmigo. Al final di: 'Estoy en coherencia.'</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Cuando tu corazón y tu mente van al mismo ritmo, todo lo demás se ordena.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Guárdalo, compártelo con alguien que necesite respirar hoy y comenta COHERENCIA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>SÁB-3</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>La creencia que no sabes que tienes</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>La creencia más peligrosa es la que no sabes que tienes.</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Haces todo 'bien', te esfuerzas, lo intentas… y algo invisible te sigue frenando.</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>No eres tú la que falla. Es un programa que aprendiste antes de poder elegirlo.</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>En espiritualidad lo llamamos programación. En psicología: aprendizaje y condicionamiento. En el Nivel 1 de Las Fórmulas Cuánticas, DESPERTAR, trabajamos los 4 estados de consciencia y el hackeo de creencias limitantes.</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>Completa esta frase sin pensar: 'Las personas como yo no pueden…'. Lo que escribas es tu creencia.</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>No puedes cambiar un programa que no ves. Verlo es el primer hackeo.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Si quieres hackear la creencia que no te deja avanzar, comenta NIVEL 1 y te mando el link de DESPERTAR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>DOM-1</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Detecta tu programa en 2 minutos</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Hoy te enseño a detectar en 2 minutos el programa que más se repite en tu vida.</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>Cambian las personas, los trabajos y las ciudades, pero sientes lo mismo una y otra vez.</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>No es mala suerte. Es un programa que se activa siempre de la misma forma.</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>En espiritualidad: programación. En psicología: aprendizaje y condicionamiento. Distintos mapas, el mismo territorio.</t>
+        </is>
+      </c>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>Responde 3 preguntas: ¿qué se repite? ¿qué siento cuando pasa? ¿dónde lo viví por primera vez?</t>
+        </is>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>Cuando ves el programa, deja de ser destino y se vuelve una elección.</t>
+        </is>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>Guárdalo para hacerlo con calma y comenta PROGRAMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>DOM-2</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Espiritualidad y ciencia no son lo mismo</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>No quiero convencerte de que la espiritualidad es ciencia. Quiero que aprendas a distinguirlas.</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>Escuchas 'está científicamente comprobado' en todos lados y ya no sabes en qué creer.</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>No tienes que elegir entre creer en todo y no creer en nada.</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
+        <is>
+          <t>La espiritualidad tiene sus propios mapas sobre consciencia y propósito. La ciencia estudia lo que se puede medir. Mi trabajo es construir el puente sin fingir que son lo mismo.</t>
+        </is>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>La próxima vez que escuches 'está comprobado', pregúntate: ¿quién lo estudió y qué midió?</t>
+        </is>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>Espiritualidad para despertar. Ciencia para comprender. Protocolos para practicar.</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>Comenta MAPAS si quieres más contenido así.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>DOM-3</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Decreto de domingo para tu semana</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Di esto el domingo en la noche y empieza tu semana en otra frecuencia.</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Guarda este video antes de que se te pierda.</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>El domingo en la noche llega la ansiedad del lunes: pendientes, cuentas, cansancio anticipado.</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>No es que odies los lunes. Es que llegas a ellos cargando la semana pasada.</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>La ciencia: tu cerebro sigue organizando lo vivido mientras duermes. En lo espiritual, un decreto es una intención dicha en voz alta.</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>Antes de dormir di: 'Esta semana elijo desde quien soy ahora, no desde quien fui. Hecho está.'</t>
+        </is>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>La semana no empieza el lunes. Empieza en lo que decides esta noche.</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>Guárdalo para cada domingo y comenta HECHO ESTÁ.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3145,7 +5072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3459,7 +5386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/nica-apify/calendario/calendario-semana-2026-10-06.xlsx
+++ b/nica-apify/calendario/calendario-semana-2026-10-06.xlsx
@@ -13,9 +13,12 @@
     <sheet name="Mi semana" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Podcast y YouTube" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Querido Ex" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Competencia" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Patrones de viralidad" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario'!$A$1:$AH$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Competencia'!$A$1:$Q$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,8 +26,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0&quot;x&quot;"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,8 +69,14 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001155CC"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -112,6 +123,11 @@
         <fgColor rgb="00F3E5F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -139,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -203,6 +219,31 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -711,7 +752,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Calendario · Guion por partes · Mi semana · Podcast y YouTube · Querido Ex (los 8 audios completos para leer y grabar).</t>
+          <t>Calendario · Guion por partes · Mi semana · Podcast y YouTube · Querido Ex · Competencia (79 piezas transcritas, con su rendimiento) · Patrones de viralidad (qué funciona, qué no, el patrón, lo que no sabemos y 3 hallazgos).</t>
         </is>
       </c>
     </row>
@@ -6036,4 +6077,7062 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q87"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="38" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Cuenta</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>PIEZA (link)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>HOOK (primera frase)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>TIPO DE HOOK</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>TEMA</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>FORMATO</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>DURACIÓN</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>EMOCIÓN</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Vistas</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Mediana de la cuenta</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>RENDIMIENTO (vistas ÷ mediana)</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>PATRÓN</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Archivo de la transcripción</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="E2" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbMptmRtnU5/</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>Las personas con TDAH no tienen un déficit de atención, tienen un exceso de atención para lo que realmente les importa.</t>
+        </is>
+      </c>
+      <c r="G2" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H2" s="20" t="inlineStr">
+        <is>
+          <t>TDAH / neurodivergencia</t>
+        </is>
+      </c>
+      <c r="I2" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J2" s="20" t="inlineStr">
+        <is>
+          <t>71 s</t>
+        </is>
+      </c>
+      <c r="K2" s="20" t="inlineStr">
+        <is>
+          <t>Sorpresa / alivio</t>
+        </is>
+      </c>
+      <c r="L2" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M2" s="24" t="n">
+        <v>2500753</v>
+      </c>
+      <c r="N2" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O2" s="25">
+        <f>IFERROR(M2/N2,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P2" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q2" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-07-25-esta-es-la-ventaja-de-las.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E3" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdXi3VJtZo0/</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Odian los ruidos fuertes, pero pueden escuchar la misma canción durante cinco horas.</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>G5 · Espejo</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>TDAH / neurodivergencia</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara rápido</t>
+        </is>
+      </c>
+      <c r="J3" s="20" t="inlineStr">
+        <is>
+          <t>34 s</t>
+        </is>
+      </c>
+      <c r="K3" s="20" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="L3" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M3" s="24" t="n">
+        <v>2166685</v>
+      </c>
+      <c r="N3" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O3" s="25">
+        <f>IFERROR(M3/N3,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P3" s="20" t="inlineStr">
+        <is>
+          <t>P5 · Lista o espejo de señales</t>
+        </is>
+      </c>
+      <c r="Q3" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-17-contradicciones-de-personas-neurodivergentes.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>@mabradiante</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mabradiante/video/7539939568632581392</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Di esto en tu casa y mira cómo todo comienza a cambiar.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>G2 · Promesa práctica</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Hogar / energía</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Cara a cámara + decreto</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>163 s</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Esperanza</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Comenta HECHO ESTÁ + guarda y comparte</t>
+        </is>
+      </c>
+      <c r="M4" s="27" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="N4" s="27" t="n">
+        <v>11850</v>
+      </c>
+      <c r="O4" s="25">
+        <f>IFERROR(M4/N4,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>P2 · Herramienta para usar ya (decreto, ritual, técnica)</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2025-08-18-di-esto-en-tu-casa-y.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZoPOQoNlb5/</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>(texto en pantalla) La física ya lo confirmó: lo que no puedes ver es lo que construye todo lo que sí ves.</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>G6 · Autoridad científica</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>Energía / despertar</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>Texto en pantalla + música</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>28 s</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>Asombro</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="M5" s="24" t="n">
+        <v>554163</v>
+      </c>
+      <c r="N5" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O5" s="25">
+        <f>IFERROR(M5/N5,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P5" s="20" t="inlineStr">
+        <is>
+          <t>P9 · Texto en pantalla + música (sin voz)</t>
+        </is>
+      </c>
+      <c r="Q5" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-06-16-la-fisica-ya-lo-confirmo.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>@mabradiante</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mabradiante/video/7278395420961688837</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Cambia tu vida con palabras gatillo: qué son, para qué sirven, cómo se hacen.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>G2 · Promesa práctica</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Espiritualidad práctica</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Cara a cámara + lista de 5</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>84 s</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Curiosidad</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Corazón y compártelo</t>
+        </is>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>628600</v>
+      </c>
+      <c r="N6" s="27" t="n">
+        <v>11850</v>
+      </c>
+      <c r="O6" s="25">
+        <f>IFERROR(M6/N6,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>P2 · Herramienta para usar ya (decreto, ritual, técnica)</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2023-09-13-cambia-tu-vida-con-palabras-gatillo.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>@mabradiante</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mabradiante/video/7460335723938385157</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Cuidado con este video porque vamos a desbloquear tu riqueza.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>G2 · Promesa práctica</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Dinero</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Cara a cámara + decreto guiado</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>145 s</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Esperanza</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Comenta YO QUIERO</t>
+        </is>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>556700</v>
+      </c>
+      <c r="N7" s="27" t="n">
+        <v>11850</v>
+      </c>
+      <c r="O7" s="25">
+        <f>IFERROR(M7/N7,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>P2 · Herramienta para usar ya (decreto, ritual, técnica)</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2025-01-16-cuidado-con-este-video-porque-vamos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc7CLvtBsBD/</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>Uno de los superpoderes de la neurodivergencia es tu capacidad de obsesionarte…</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>TDAH / neurodivergencia</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>83 s</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>Orgullo</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M8" s="24" t="n">
+        <v>171167</v>
+      </c>
+      <c r="N8" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O8" s="25">
+        <f>IFERROR(M8/N8,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P8" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q8" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-05-este-es-uno-de-los-super.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddwnt0FPrfM/</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>(caption) Cuando entrenas lo suficiente a tu atención para acompañarte…</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>G2 · Práctica</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>Emociones / presencia</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>Texto en pantalla + música</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>46 s</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="M9" s="24" t="n">
+        <v>174917</v>
+      </c>
+      <c r="N9" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O9" s="25">
+        <f>IFERROR(M9/N9,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P9" s="20" t="inlineStr">
+        <is>
+          <t>P9 · Texto en pantalla + música (sin voz)</t>
+        </is>
+      </c>
+      <c r="Q9" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-26-cuando-entrenas-lo-suficiente-a-tu.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcUlSiytrS_/</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter es el ejemplo perfecto de cómo funciona la manifestación.</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>G9 · Ejemplo famoso</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>Manifestación / identidad</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>51 s</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>Inspiración</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M10" s="24" t="n">
+        <v>144483</v>
+      </c>
+      <c r="N10" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O10" s="25">
+        <f>IFERROR(M10/N10,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P10" s="20" t="inlineStr">
+        <is>
+          <t>P7 · Autoridad: estudio, famoso o cita</t>
+        </is>
+      </c>
+      <c r="Q10" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-08-22-sabrina-carpenter-es-el-ejemplo-perfecto.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcC8I3KN9kI/</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>Alguien dijo que las personas con la forma de pensar más avanzada tienen una habilidad muy particular.</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>G6 · Autoridad</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>Identidad / inteligencia</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>45 s</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>Orgullo / curiosidad</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>Compártelo</t>
+        </is>
+      </c>
+      <c r="M11" s="24" t="n">
+        <v>127947</v>
+      </c>
+      <c r="N11" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O11" s="25">
+        <f>IFERROR(M11/N11,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P11" s="20" t="inlineStr">
+        <is>
+          <t>P7 · Autoridad: estudio, famoso o cita</t>
+        </is>
+      </c>
+      <c r="Q11" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-08-15-esta-es-la-manera-de-pensar.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcxHcIpN2jw/</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>Solo existen dos tipos de personas que ganan en la vida.</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>G5 · Lista</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>Metas / éxito</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>50 s</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>Curiosidad</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M12" s="24" t="n">
+        <v>121918</v>
+      </c>
+      <c r="N12" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O12" s="25">
+        <f>IFERROR(M12/N12,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P12" s="20" t="inlineStr">
+        <is>
+          <t>P5 · Lista o espejo de señales</t>
+        </is>
+      </c>
+      <c r="Q12" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-02-que-tipo-de-persona-eres.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>@mabradiante</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mabradiante/video/7491928239577861382</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Cuidado con este video porque esta es una oración para conectar con la abundancia.</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>G2 · Promesa práctica</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Dinero / abundancia</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Cara a cámara + oración guiada</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>176 s</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Esperanza</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Mensaje a Instagram (e-book gratis)</t>
+        </is>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>335300</v>
+      </c>
+      <c r="N13" s="27" t="n">
+        <v>11850</v>
+      </c>
+      <c r="O13" s="25">
+        <f>IFERROR(M13/N13,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>P2 · Herramienta para usar ya (decreto, ritual, técnica)</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2025-04-11-cuidado-con-este-video-porque-esta.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdfGwrrvq_o/</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>Las personas más inteligentes que conozco tienen un problema rarísimo.</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>Constancia / inteligencia</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>77 s</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>Curiosidad</t>
+        </is>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M14" s="24" t="n">
+        <v>101223</v>
+      </c>
+      <c r="N14" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O14" s="25">
+        <f>IFERROR(M14/N14,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P14" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q14" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-19-esta-es-una-de-las-mayores.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>@mabradiante</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mabradiante/video/7459976432870034693</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Cuidado con este video porque vamos a activar tu ADN del dinero.</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>G2 · Promesa práctica</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Dinero</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Cara a cámara + decreto guiado</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>111 s</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Esperanza</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Hecho está + compártelo</t>
+        </is>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>280200</v>
+      </c>
+      <c r="N15" s="27" t="n">
+        <v>11850</v>
+      </c>
+      <c r="O15" s="25">
+        <f>IFERROR(M15/N15,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>P2 · Herramienta para usar ya (decreto, ritual, técnica)</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2025-01-15-cuidado-con-este-video-porque-vamos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dcch8c_tibs/</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>La frecuencia del TDA te puede hacer ganar muchísimo dinero.</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>TDAH + dinero</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>58 s</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>Esperanza</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M16" s="24" t="n">
+        <v>79118</v>
+      </c>
+      <c r="N16" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O16" s="25">
+        <f>IFERROR(M16/N16,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P16" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q16" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-08-25-el-tdah-te-puede-generar-mucho.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>PsicoespacioVe</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/1082191651093348/</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>No arregles a la persona con la que estás saliendo.</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>51 s</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>Sorpresa / identificación</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>Comenta CLASE</t>
+        </is>
+      </c>
+      <c r="M17" s="24" t="n">
+        <v>46000</v>
+      </c>
+      <c r="N17" s="24" t="n">
+        <v>2375</v>
+      </c>
+      <c r="O17" s="25">
+        <f>IFERROR(M17/N17,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P17" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q17" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/facebook-no-arregles-a-la-persona-con-la-que-estas-saliendo.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdhoB0yO6lu/</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>(caption) Hay muchas formas de huir de la incomodidad, pero pocos se entrenan para atravesarla.</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>Emociones / incomodidad</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>Texto en pantalla + música</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>28 s</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="M18" s="24" t="n">
+        <v>86690</v>
+      </c>
+      <c r="N18" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O18" s="25">
+        <f>IFERROR(M18/N18,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P18" s="20" t="inlineStr">
+        <is>
+          <t>P9 · Texto en pantalla + música (sin voz)</t>
+        </is>
+      </c>
+      <c r="Q18" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-20-hay-muchas-formas-de-huir-de.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc9upGuNmvR/</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>¿Y si el TDAH no fuera simplemente un trastorno?</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>G4 · Pregunta</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>TDAH / neurodivergencia</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>71 s</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>Esperanza</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>Comenta NEUROSPICY</t>
+        </is>
+      </c>
+      <c r="M19" s="24" t="n">
+        <v>74380</v>
+      </c>
+      <c r="N19" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O19" s="25">
+        <f>IFERROR(M19/N19,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P19" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q19" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-06-y-si-el-tdah-no-fuera.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dchq2qitF5k/</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>Me di cuenta de que si tienes TDA, en realidad tienes una ventaja.</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>TDAH / neurodivergencia</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>50 s</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>Alivio</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M20" s="24" t="n">
+        <v>63330</v>
+      </c>
+      <c r="N20" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O20" s="25">
+        <f>IFERROR(M20/N20,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P20" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q20" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-08-27-si-tienes-tdah-en-realidad-tienes.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dd9-wCCMwLn/</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>Una de las señales más claras de inteligencia emocional es no necesitar destruir a alguien para decirle una verdad.</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>G5 · Señal</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>Inteligencia emocional</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>50 s</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>Orgullo</t>
+        </is>
+      </c>
+      <c r="L21" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M21" s="24" t="n">
+        <v>61427</v>
+      </c>
+      <c r="N21" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O21" s="25">
+        <f>IFERROR(M21/N21,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P21" s="20" t="inlineStr">
+        <is>
+          <t>P5 · Lista o espejo de señales</t>
+        </is>
+      </c>
+      <c r="Q21" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-10-01-esta-es-la-senal-mas-clara.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>PsicoespacioVe</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/1645012720383908/</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>Los bonsáis no simplemente son árboles que nacieron enanos.</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>G7 · Metáfora visual</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>Identidad / potencial</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>Fragmento de clase en vivo</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>96 s</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>Esperanza</t>
+        </is>
+      </c>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>Comenta CLASE</t>
+        </is>
+      </c>
+      <c r="M22" s="24" t="n">
+        <v>34000</v>
+      </c>
+      <c r="N22" s="24" t="n">
+        <v>2375</v>
+      </c>
+      <c r="O22" s="25">
+        <f>IFERROR(M22/N22,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P22" s="20" t="inlineStr">
+        <is>
+          <t>P6 · Historia o metáfora</t>
+        </is>
+      </c>
+      <c r="Q22" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/facebook-patron-bonsai-clase-1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DeDVDapNi3P/</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>Las personas más inteligentes que he conocido tienen algo en común que la sociedad confunde con debilidad.</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>G6 · Cita (Fitzgerald)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>Identidad / inteligencia</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>68 s</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>Orgullo</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M23" s="24" t="n">
+        <v>52578</v>
+      </c>
+      <c r="N23" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O23" s="25">
+        <f>IFERROR(M23/N23,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P23" s="20" t="inlineStr">
+        <is>
+          <t>P7 · Autoridad: estudio, famoso o cita</t>
+        </is>
+      </c>
+      <c r="Q23" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-10-04-este-es-el-factor-comun-de.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcKYbr2txl3/</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>¿Cómo sabes si realmente tienes TDAH o simplemente estás distraído?</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>G4 · Pregunta-dolor</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>TDAH / neurodivergencia</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>61 s</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>Curiosidad</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>Busca un profesional</t>
+        </is>
+      </c>
+      <c r="M24" s="24" t="n">
+        <v>45105</v>
+      </c>
+      <c r="N24" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O24" s="25">
+        <f>IFERROR(M24/N24,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P24" s="20" t="inlineStr">
+        <is>
+          <t>P3 · Dolor en sus palabras + explicación</t>
+        </is>
+      </c>
+      <c r="Q24" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-08-18-esta-es-la-forma-de-saber.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>@transformacion_acelerada</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>2023-08-18</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@transformacion_acelerada/video/7268674262804811014</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>¿Por qué sigo sin soltar a una persona o a una situación que me está haciendo daño?</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>G4 · Pregunta-dolor</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones / apego</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara, 3 razones + tips</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>238 s</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>Sígueme para más</t>
+        </is>
+      </c>
+      <c r="M25" s="24" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="N25" s="24" t="n">
+        <v>295900</v>
+      </c>
+      <c r="O25" s="25">
+        <f>IFERROR(M25/N25,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P25" s="20" t="inlineStr">
+        <is>
+          <t>P3 · Dolor en sus palabras + explicación</t>
+        </is>
+      </c>
+      <c r="Q25" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2023-08-18-por-que-sigo-sin-soltar-a.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdDLmxntJct/</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>Lady Gaga es uno de los ejemplos más claros de cómo funciona la manifestación.</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>G9 · Ejemplo famoso</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>Manifestación / identidad</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>53 s</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>Inspiración</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M26" s="24" t="n">
+        <v>30983</v>
+      </c>
+      <c r="N26" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O26" s="25">
+        <f>IFERROR(M26/N26,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P26" s="20" t="inlineStr">
+        <is>
+          <t>P7 · Autoridad: estudio, famoso o cita</t>
+        </is>
+      </c>
+      <c r="Q26" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-09-esta-es-la-manifestacion-que-usaba.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dce-DS8Nogg/</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>El 99% de tu éxito depende de una sola cosa.</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>G6 · Autoridad (Harvard)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>Metas / entorno</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>71 s</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>Curiosidad</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M27" s="24" t="n">
+        <v>28127</v>
+      </c>
+      <c r="N27" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O27" s="25">
+        <f>IFERROR(M27/N27,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P27" s="20" t="inlineStr">
+        <is>
+          <t>P7 · Autoridad: estudio, famoso o cita</t>
+        </is>
+      </c>
+      <c r="Q27" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-08-26-tu-exito-depende-99-de-este.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>@transformacion_acelerada</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>2022-10-23</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@transformacion_acelerada/video/7157777541065919750</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>(texto en pantalla) 4 señales de que el universo quiere darte lo que has pedido</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>G5 · Lista de señales</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>Manifestación / cambio</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>Texto en pantalla + música + gestos</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>59 s</t>
+        </is>
+      </c>
+      <c r="K28" s="20" t="inlineStr">
+        <is>
+          <t>Esperanza</t>
+        </is>
+      </c>
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M28" s="24" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="N28" s="24" t="n">
+        <v>295900</v>
+      </c>
+      <c r="O28" s="25">
+        <f>IFERROR(M28/N28,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P28" s="20" t="inlineStr">
+        <is>
+          <t>P9 · Texto en pantalla + música (sin voz)</t>
+        </is>
+      </c>
+      <c r="Q28" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2022-10-23-senales-universo-quiere-darte-lo-que-pediste.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>PsicoespacioVe</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/1988925101818211/</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>Les voy a dar un regalo… hay un programa gratuito…</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>Anuncio</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>Reprogramar la mente</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara corto</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>26 s</t>
+        </is>
+      </c>
+      <c r="K29" s="20" t="inlineStr">
+        <is>
+          <t>Curiosidad</t>
+        </is>
+      </c>
+      <c r="L29" s="20" t="inlineStr">
+        <is>
+          <t>Comenta REPROGRÁMATE</t>
+        </is>
+      </c>
+      <c r="M29" s="24" t="n">
+        <v>15000</v>
+      </c>
+      <c r="N29" s="24" t="n">
+        <v>2375</v>
+      </c>
+      <c r="O29" s="25">
+        <f>IFERROR(M29/N29,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P29" s="20" t="inlineStr">
+        <is>
+          <t>P8 · Anuncio directo de evento o producto</t>
+        </is>
+      </c>
+      <c r="Q29" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/facebook-hoy-comienza-reprogramate.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdR_B07ujiq/</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>(caption) Cada vez que te peleas con la realidad, no solo la realidad no cambia…</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>Aceptación / energía</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>Texto en pantalla + música</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
+        <is>
+          <t>9 s</t>
+        </is>
+      </c>
+      <c r="K30" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="M30" s="24" t="n">
+        <v>25972</v>
+      </c>
+      <c r="N30" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O30" s="25">
+        <f>IFERROR(M30/N30,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P30" s="20" t="inlineStr">
+        <is>
+          <t>P9 · Texto en pantalla + música (sin voz)</t>
+        </is>
+      </c>
+      <c r="Q30" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-14-cada-vez-que-te-peleas-con.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdrZT_hBMqs/</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>(caption) Controlarlo TODO y ganarle a la realidad es una batalla que no vas a ganar, NUNCA.</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>Control / ansiedad</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>Texto en pantalla + música</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>5 s</t>
+        </is>
+      </c>
+      <c r="K31" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="L31" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="M31" s="24" t="n">
+        <v>24349</v>
+      </c>
+      <c r="N31" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O31" s="25">
+        <f>IFERROR(M31/N31,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P31" s="20" t="inlineStr">
+        <is>
+          <t>P9 · Texto en pantalla + música (sin voz)</t>
+        </is>
+      </c>
+      <c r="Q31" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-24-controlarlo-todo-y-ganarle-a-la.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdZUNPuBLso/</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>(caption) Cuando dejas de identificarte con las identidades, historias y creencias de siempre… EVOLUCIONAS.</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>Identidad / despertar</t>
+        </is>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
+        <is>
+          <t>Texto en pantalla + música</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
+        <is>
+          <t>6 s</t>
+        </is>
+      </c>
+      <c r="K32" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="L32" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="M32" s="24" t="n">
+        <v>24317</v>
+      </c>
+      <c r="N32" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O32" s="25">
+        <f>IFERROR(M32/N32,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P32" s="20" t="inlineStr">
+        <is>
+          <t>P9 · Texto en pantalla + música (sin voz)</t>
+        </is>
+      </c>
+      <c r="Q32" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-17-cuando-dejas-de-identificarte-con-las.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>@manifestadoras</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>2022-01-21</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@manifestadoras/video/7055677548180540678</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>Hoy te voy a enseñar una técnica para que una persona se contacte con vos.</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>G3 · Técnica paso a paso</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones / manifestar</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara + técnica guiada</t>
+        </is>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>178 s</t>
+        </is>
+      </c>
+      <c r="K33" s="20" t="inlineStr">
+        <is>
+          <t>Esperanza</t>
+        </is>
+      </c>
+      <c r="L33" s="20" t="inlineStr">
+        <is>
+          <t>Cuéntame en comentarios si te funcionó</t>
+        </is>
+      </c>
+      <c r="M33" s="24" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="N33" s="24" t="n">
+        <v>674000</v>
+      </c>
+      <c r="O33" s="25">
+        <f>IFERROR(M33/N33,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P33" s="20" t="inlineStr">
+        <is>
+          <t>P2 · Herramienta para usar ya (decreto, ritual, técnica)</t>
+        </is>
+      </c>
+      <c r="Q33" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2022-01-21-hoy-te-voy-a-ensenar-una.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcysjR-MHRc/</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>(caption) ¿Ya estás dentro del Taller Sana tu Niño Interno?</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>Anuncio</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>Niño interno / taller</t>
+        </is>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
+        <is>
+          <t>Texto en pantalla + música</t>
+        </is>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>11 s</t>
+        </is>
+      </c>
+      <c r="K34" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="L34" s="20" t="inlineStr">
+        <is>
+          <t>Taller</t>
+        </is>
+      </c>
+      <c r="M34" s="24" t="n">
+        <v>23295</v>
+      </c>
+      <c r="N34" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O34" s="25">
+        <f>IFERROR(M34/N34,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P34" s="20" t="inlineStr">
+        <is>
+          <t>P9 · Texto en pantalla + música (sin voz)</t>
+        </is>
+      </c>
+      <c r="Q34" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-02-ya-estas-dentro-del-taller-sana.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>@soylizadebri</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@soylizadebri/video/7647697725454109960</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>No es que no te elijan, es que tu identidad está construida para que no te elijan.</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones / no me eligen</t>
+        </is>
+      </c>
+      <c r="I35" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara + anécdota</t>
+        </is>
+      </c>
+      <c r="J35" s="20" t="inlineStr">
+        <is>
+          <t>246 s</t>
+        </is>
+      </c>
+      <c r="K35" s="20" t="inlineStr">
+        <is>
+          <t>Sorpresa</t>
+        </is>
+      </c>
+      <c r="L35" s="20" t="inlineStr">
+        <is>
+          <t>Reto de 21 días (link en perfil)</t>
+        </is>
+      </c>
+      <c r="M35" s="24" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="N35" s="24" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="O35" s="25">
+        <f>IFERROR(M35/N35,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P35" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q35" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2026-06-05-no-es-que-no-te-elijan.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dd4JR9zgxlV/</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>(caption) Perder personas durante tu proceso de evolución no es lo más doloroso que vas a experimentar…</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones / evolución</t>
+        </is>
+      </c>
+      <c r="I36" s="20" t="inlineStr">
+        <is>
+          <t>Texto en pantalla + música</t>
+        </is>
+      </c>
+      <c r="J36" s="20" t="inlineStr">
+        <is>
+          <t>5 s</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="M36" s="24" t="n">
+        <v>18203</v>
+      </c>
+      <c r="N36" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O36" s="25">
+        <f>IFERROR(M36/N36,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P36" s="20" t="inlineStr">
+        <is>
+          <t>P9 · Texto en pantalla + música (sin voz)</t>
+        </is>
+      </c>
+      <c r="Q36" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-29-perder-personas-durante-tu-proceso-de.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcpbmGgtmyF/</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>Quiero ganar mucho más dinero, entonces deja de hacerte pequeña…</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>Dinero / TDAH</t>
+        </is>
+      </c>
+      <c r="I37" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J37" s="20" t="inlineStr">
+        <is>
+          <t>75 s</t>
+        </is>
+      </c>
+      <c r="K37" s="20" t="inlineStr">
+        <is>
+          <t>Confrontación</t>
+        </is>
+      </c>
+      <c r="L37" s="20" t="inlineStr">
+        <is>
+          <t>Comenta VIDEO</t>
+        </is>
+      </c>
+      <c r="M37" s="24" t="n">
+        <v>14986</v>
+      </c>
+      <c r="N37" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O37" s="25">
+        <f>IFERROR(M37/N37,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P37" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q37" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-08-30-todos-vivimos-situaciones-similares-pero-las.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dde1nKMNHwT/</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>(caption) Tal vez hayas sentido esa "libertad" una vez que dejaste esa relación, ese empleo…</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>G4 · Espejo</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>Cambio / huida</t>
+        </is>
+      </c>
+      <c r="I38" s="20" t="inlineStr">
+        <is>
+          <t>Texto en pantalla + música</t>
+        </is>
+      </c>
+      <c r="J38" s="20" t="inlineStr">
+        <is>
+          <t>5 s</t>
+        </is>
+      </c>
+      <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="M38" s="24" t="n">
+        <v>16103</v>
+      </c>
+      <c r="N38" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O38" s="25">
+        <f>IFERROR(M38/N38,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P38" s="20" t="inlineStr">
+        <is>
+          <t>P9 · Texto en pantalla + música (sin voz)</t>
+        </is>
+      </c>
+      <c r="Q38" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-19-tal-vez-hayas-sentido-esa-libertad.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>@manifestadoras</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@manifestadoras/video/7288714702434077958</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>La frase "todos vuelven" es la prueba de que el desapego es la clave del magnetismo.</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones / ex</t>
+        </is>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J39" s="20" t="inlineStr">
+        <is>
+          <t>114 s</t>
+        </is>
+      </c>
+      <c r="K39" s="20" t="inlineStr">
+        <is>
+          <t>Esperanza</t>
+        </is>
+      </c>
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>Membresía (link en perfil)</t>
+        </is>
+      </c>
+      <c r="M39" s="24" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="N39" s="24" t="n">
+        <v>674000</v>
+      </c>
+      <c r="O39" s="25">
+        <f>IFERROR(M39/N39,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P39" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q39" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2023-10-11-la-frase-todos-vuelven-es-la.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>@transformacion_acelerada</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>2022-04-25</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@transformacion_acelerada/video/7090658363779910917</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>Te lo digo crudo y sin rodeos.</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>G10 · Reacción / dúo</t>
+        </is>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones</t>
+        </is>
+      </c>
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t>Dúo: pantalla dividida + carteles</t>
+        </is>
+      </c>
+      <c r="J40" s="20" t="inlineStr">
+        <is>
+          <t>51 s</t>
+        </is>
+      </c>
+      <c r="K40" s="20" t="inlineStr">
+        <is>
+          <t>Validación</t>
+        </is>
+      </c>
+      <c r="L40" s="20" t="inlineStr">
+        <is>
+          <t>Coméntame un SÍ</t>
+        </is>
+      </c>
+      <c r="M40" s="24" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="N40" s="24" t="n">
+        <v>295900</v>
+      </c>
+      <c r="O40" s="25">
+        <f>IFERROR(M40/N40,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P40" s="20" t="inlineStr">
+        <is>
+          <t>P4 · Reacción a video ajeno de dolor o polémica</t>
+        </is>
+      </c>
+      <c r="Q40" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2022-04-25-te-lo-digo-crudo-y-sin-rodeos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>@manifestadoras</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@manifestadoras/video/7103156957284011269</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>La atracción es energética, no física.</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones</t>
+        </is>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara íntimo</t>
+        </is>
+      </c>
+      <c r="J41" s="20" t="inlineStr">
+        <is>
+          <t>176 s</t>
+        </is>
+      </c>
+      <c r="K41" s="20" t="inlineStr">
+        <is>
+          <t>Sorpresa</t>
+        </is>
+      </c>
+      <c r="L41" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M41" s="24" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="N41" s="24" t="n">
+        <v>674000</v>
+      </c>
+      <c r="O41" s="25">
+        <f>IFERROR(M41/N41,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P41" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q41" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2022-05-29-la-atraccion-es-energetica-no-fisica.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>@transformacion_acelerada</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@transformacion_acelerada/video/7360331779762343173</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>Tus hijos no son tu razón para quedarte, son tu pretexto.</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones / maternidad</t>
+        </is>
+      </c>
+      <c r="I42" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara + carteles numerados</t>
+        </is>
+      </c>
+      <c r="J42" s="20" t="inlineStr">
+        <is>
+          <t>155 s</t>
+        </is>
+      </c>
+      <c r="K42" s="20" t="inlineStr">
+        <is>
+          <t>Confrontación</t>
+        </is>
+      </c>
+      <c r="L42" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M42" s="24" t="n">
+        <v>954700</v>
+      </c>
+      <c r="N42" s="24" t="n">
+        <v>295900</v>
+      </c>
+      <c r="O42" s="25">
+        <f>IFERROR(M42/N42,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P42" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q42" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2024-04-21-tus-hijos-no-son-tu-razon.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>@soylizadebri</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@soylizadebri/video/7604271995743866130</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>Mi mayor turn off de las muchachas es cuando tienen Instagram… (video ajeno)</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>G10 · Reacción / stitch</t>
+        </is>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones / autonomía</t>
+        </is>
+      </c>
+      <c r="I43" s="20" t="inlineStr">
+        <is>
+          <t>Reacción intercalada</t>
+        </is>
+      </c>
+      <c r="J43" s="20" t="inlineStr">
+        <is>
+          <t>298 s</t>
+        </is>
+      </c>
+      <c r="K43" s="20" t="inlineStr">
+        <is>
+          <t>Indignación</t>
+        </is>
+      </c>
+      <c r="L43" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M43" s="24" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="N43" s="24" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="O43" s="25">
+        <f>IFERROR(M43/N43,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P43" s="20" t="inlineStr">
+        <is>
+          <t>P4 · Reacción a video ajeno de dolor o polémica</t>
+        </is>
+      </c>
+      <c r="Q43" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2026-02-07-reaccion-turn-off-mujeres-que-viajan-solas.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>@soylizadebri</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@soylizadebri/video/7472436568557489414</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>Solo voy a tirar un facto de persona que se ha operado.</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>G11 · Confesión + polémica</t>
+        </is>
+      </c>
+      <c r="H44" s="20" t="inlineStr">
+        <is>
+          <t>Cuerpo / críticas</t>
+        </is>
+      </c>
+      <c r="I44" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J44" s="20" t="inlineStr">
+        <is>
+          <t>161 s</t>
+        </is>
+      </c>
+      <c r="K44" s="20" t="inlineStr">
+        <is>
+          <t>Polémica</t>
+        </is>
+      </c>
+      <c r="L44" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M44" s="24" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="N44" s="24" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="O44" s="25">
+        <f>IFERROR(M44/N44,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P44" s="20" t="inlineStr">
+        <is>
+          <t>P4 · Reacción a video ajeno de dolor o polémica</t>
+        </is>
+      </c>
+      <c r="Q44" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2025-02-17-solo-voy-a-tirar-un-facto.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc-BvqcP2qM/</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>(caption) Si en tu familia te llaman "rebelde", "difícil", "incómodx", no te sientas mal…</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
+        <is>
+          <t>Familia / identidad</t>
+        </is>
+      </c>
+      <c r="I45" s="20" t="inlineStr">
+        <is>
+          <t>Texto en pantalla + música</t>
+        </is>
+      </c>
+      <c r="J45" s="20" t="inlineStr">
+        <is>
+          <t>7 s</t>
+        </is>
+      </c>
+      <c r="K45" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="L45" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="M45" s="24" t="n">
+        <v>13212</v>
+      </c>
+      <c r="N45" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O45" s="25">
+        <f>IFERROR(M45/N45,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P45" s="20" t="inlineStr">
+        <is>
+          <t>P9 · Texto en pantalla + música (sin voz)</t>
+        </is>
+      </c>
+      <c r="Q45" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-07-si-en-tu-familia-te-llaman.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcoYlduu25D/</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>(caption) Las únicas señales que las heridas emocionales te dan son los triggers.</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H46" s="20" t="inlineStr">
+        <is>
+          <t>Heridas / sanación</t>
+        </is>
+      </c>
+      <c r="I46" s="20" t="inlineStr">
+        <is>
+          <t>Texto en pantalla + música</t>
+        </is>
+      </c>
+      <c r="J46" s="20" t="inlineStr">
+        <is>
+          <t>10 s</t>
+        </is>
+      </c>
+      <c r="K46" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="L46" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="M46" s="24" t="n">
+        <v>12868</v>
+      </c>
+      <c r="N46" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O46" s="25">
+        <f>IFERROR(M46/N46,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P46" s="20" t="inlineStr">
+        <is>
+          <t>P9 · Texto en pantalla + música (sin voz)</t>
+        </is>
+      </c>
+      <c r="Q46" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-08-29-las-unicas-senales-que-las-heridas.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcaAYovNh1c/</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>¿Te ha pasado que dicen que te estás dejando?</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>G5 · Espejo</t>
+        </is>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
+        <is>
+          <t>Autoestima / juicio ajeno</t>
+        </is>
+      </c>
+      <c r="I47" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J47" s="20" t="inlineStr">
+        <is>
+          <t>60 s</t>
+        </is>
+      </c>
+      <c r="K47" s="20" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M47" s="24" t="n">
+        <v>11245</v>
+      </c>
+      <c r="N47" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O47" s="25">
+        <f>IFERROR(M47/N47,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P47" s="20" t="inlineStr">
+        <is>
+          <t>P5 · Lista o espejo de señales</t>
+        </is>
+      </c>
+      <c r="Q47" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-08-24-hagas-lo-que-hagas-siempre-te.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>@soylizadebri</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@soylizadebri/video/7631305601934462215</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>Me han amado, pero nunca me han elegido. (video ajeno) / ¿Eres la mujer que todo el mundo quiere pero no se quedan?</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>G10 · Reacción + G4</t>
+        </is>
+      </c>
+      <c r="H48" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones / no me eligen</t>
+        </is>
+      </c>
+      <c r="I48" s="20" t="inlineStr">
+        <is>
+          <t>Pantalla verde + cara a cámara largo</t>
+        </is>
+      </c>
+      <c r="J48" s="20" t="inlineStr">
+        <is>
+          <t>429 s</t>
+        </is>
+      </c>
+      <c r="K48" s="20" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="L48" s="20" t="inlineStr">
+        <is>
+          <t>Reto de 21 días (link en perfil)</t>
+        </is>
+      </c>
+      <c r="M48" s="24" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="N48" s="24" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="O48" s="25">
+        <f>IFERROR(M48/N48,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P48" s="20" t="inlineStr">
+        <is>
+          <t>P4 · Reacción a video ajeno de dolor o polémica</t>
+        </is>
+      </c>
+      <c r="Q48" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2026-04-21-eres-la-mujer-que-nunca-eligen.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>@manifestadoras</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@manifestadoras/video/7269511948922866950</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>Vamos a hablar de cómo sanar la herida de abandono… la persona no es tu tipo, es tu trauma.</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones / abandono</t>
+        </is>
+      </c>
+      <c r="I49" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara largo (8 min)</t>
+        </is>
+      </c>
+      <c r="J49" s="20" t="inlineStr">
+        <is>
+          <t>475 s</t>
+        </is>
+      </c>
+      <c r="K49" s="20" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="L49" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M49" s="24" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="N49" s="24" t="n">
+        <v>674000</v>
+      </c>
+      <c r="O49" s="25">
+        <f>IFERROR(M49/N49,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P49" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q49" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2023-08-20-vamos-a-hablar-de-como-sanar.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>@soylizadebri</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@soylizadebri/video/7653600946005511432</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>¿Cómo no voy a pensar que el problema sea yo si nunca me eligen? (video ajeno llorando)</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="inlineStr">
+        <is>
+          <t>G10 · Reacción + G4</t>
+        </is>
+      </c>
+      <c r="H50" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones / no me eligen</t>
+        </is>
+      </c>
+      <c r="I50" s="20" t="inlineStr">
+        <is>
+          <t>Pantalla verde + cara a cámara largo</t>
+        </is>
+      </c>
+      <c r="J50" s="20" t="inlineStr">
+        <is>
+          <t>456 s</t>
+        </is>
+      </c>
+      <c r="K50" s="20" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="L50" s="20" t="inlineStr">
+        <is>
+          <t>Reto de 21 días (link en perfil)</t>
+        </is>
+      </c>
+      <c r="M50" s="24" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="N50" s="24" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="O50" s="25">
+        <f>IFERROR(M50/N50,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P50" s="20" t="inlineStr">
+        <is>
+          <t>P4 · Reacción a video ajeno de dolor o polémica</t>
+        </is>
+      </c>
+      <c r="Q50" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2026-06-20-por-que-eres-la-mujer-a-la-que-nunca-eligen.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Ddy9JVOpxcU/</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>Cuando no sabes sostener lo que sientes, tampoco vas a poder cargar con los deseos del corazón.</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>Deseos / emociones</t>
+        </is>
+      </c>
+      <c r="I51" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara largo</t>
+        </is>
+      </c>
+      <c r="J51" s="20" t="inlineStr">
+        <is>
+          <t>166 s</t>
+        </is>
+      </c>
+      <c r="K51" s="20" t="inlineStr">
+        <is>
+          <t>Confrontación</t>
+        </is>
+      </c>
+      <c r="L51" s="20" t="inlineStr">
+        <is>
+          <t>Comenta SESIÓN</t>
+        </is>
+      </c>
+      <c r="M51" s="24" t="n">
+        <v>11866</v>
+      </c>
+      <c r="N51" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O51" s="25">
+        <f>IFERROR(M51/N51,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P51" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q51" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-27-hay-una-diferencia-brutal-entre-desear.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DeAC0yMNK6c/</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>Vengo a romper el gran mito que hay alrededor de sanar.</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>Sanación</t>
+        </is>
+      </c>
+      <c r="I52" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara largo</t>
+        </is>
+      </c>
+      <c r="J52" s="20" t="inlineStr">
+        <is>
+          <t>142 s</t>
+        </is>
+      </c>
+      <c r="K52" s="20" t="inlineStr">
+        <is>
+          <t>Alivio</t>
+        </is>
+      </c>
+      <c r="L52" s="20" t="inlineStr">
+        <is>
+          <t>Comenta QLT</t>
+        </is>
+      </c>
+      <c r="M52" s="24" t="n">
+        <v>11494</v>
+      </c>
+      <c r="N52" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O52" s="25">
+        <f>IFERROR(M52/N52,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P52" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q52" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-10-02-puedes-pasar-anos-buscando-la-tecnica.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>@manifestadoras</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>2023-02-22</t>
+        </is>
+      </c>
+      <c r="E53" s="23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@manifestadoras/video/7202984141573344517</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>Todo el mundo habla del lucky girl syndrome, pero nadie te explica cómo convertirte en esa chica.</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>G3 · Técnica paso a paso</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>Manifestación / suerte</t>
+        </is>
+      </c>
+      <c r="I53" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara + pantalla de laptop</t>
+        </is>
+      </c>
+      <c r="J53" s="20" t="inlineStr">
+        <is>
+          <t>177 s</t>
+        </is>
+      </c>
+      <c r="K53" s="20" t="inlineStr">
+        <is>
+          <t>Curiosidad</t>
+        </is>
+      </c>
+      <c r="L53" s="20" t="inlineStr">
+        <is>
+          <t>Canal de YouTube</t>
+        </is>
+      </c>
+      <c r="M53" s="24" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="N53" s="24" t="n">
+        <v>674000</v>
+      </c>
+      <c r="O53" s="25">
+        <f>IFERROR(M53/N53,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P53" s="20" t="inlineStr">
+        <is>
+          <t>P2 · Herramienta para usar ya (decreto, ritual, técnica)</t>
+        </is>
+      </c>
+      <c r="Q53" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/tiktok-2023-02-22-todo-el-mundo-habla-del-lucky.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E54" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdcrJSjttQ2/</t>
+        </is>
+      </c>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>No fue tu responsabilidad que ciertas cosas pasaran, pero sí es tu responsabilidad qué haces con ellas ahora.</t>
+        </is>
+      </c>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H54" s="20" t="inlineStr">
+        <is>
+          <t>Neurodivergencia / responsabilidad</t>
+        </is>
+      </c>
+      <c r="I54" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J54" s="20" t="inlineStr">
+        <is>
+          <t>77 s</t>
+        </is>
+      </c>
+      <c r="K54" s="20" t="inlineStr">
+        <is>
+          <t>Alivio</t>
+        </is>
+      </c>
+      <c r="L54" s="20" t="inlineStr">
+        <is>
+          <t>Comenta PODER</t>
+        </is>
+      </c>
+      <c r="M54" s="24" t="n">
+        <v>9799</v>
+      </c>
+      <c r="N54" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O54" s="25">
+        <f>IFERROR(M54/N54,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P54" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q54" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-19-no-fue-tu-responsabilidad-que-ciertas.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DczOVOfsJo6/</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>Las personas ricas no tienen más disciplina, tienen una idea diferente de lo que es normal.</t>
+        </is>
+      </c>
+      <c r="G55" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H55" s="20" t="inlineStr">
+        <is>
+          <t>Dinero</t>
+        </is>
+      </c>
+      <c r="I55" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J55" s="20" t="inlineStr">
+        <is>
+          <t>60 s</t>
+        </is>
+      </c>
+      <c r="K55" s="20" t="inlineStr">
+        <is>
+          <t>Sorpresa</t>
+        </is>
+      </c>
+      <c r="L55" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M55" s="24" t="n">
+        <v>9481</v>
+      </c>
+      <c r="N55" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O55" s="25">
+        <f>IFERROR(M55/N55,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P55" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q55" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-02-la-mayoria-de-las-personas-ricas.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E56" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdaQdkCNeLr/</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>¿Tienes TDAH y sigues diciendo "así soy yo"?</t>
+        </is>
+      </c>
+      <c r="G56" s="20" t="inlineStr">
+        <is>
+          <t>G4 · Pregunta-dolor</t>
+        </is>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
+        <is>
+          <t>TDAH / responsabilidad</t>
+        </is>
+      </c>
+      <c r="I56" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J56" s="20" t="inlineStr">
+        <is>
+          <t>84 s</t>
+        </is>
+      </c>
+      <c r="K56" s="20" t="inlineStr">
+        <is>
+          <t>Confrontación</t>
+        </is>
+      </c>
+      <c r="L56" s="20" t="inlineStr">
+        <is>
+          <t>Comenta PODER</t>
+        </is>
+      </c>
+      <c r="M56" s="24" t="n">
+        <v>9366</v>
+      </c>
+      <c r="N56" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O56" s="25">
+        <f>IFERROR(M56/N56,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P56" s="20" t="inlineStr">
+        <is>
+          <t>P3 · Dolor en sus palabras + explicación</t>
+        </is>
+      </c>
+      <c r="Q56" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-18-comenta-poder-y-te-envio-el.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E57" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcXb_yLNnb6/</t>
+        </is>
+      </c>
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>No puedes ser realmente feliz con un hombre si antes no sabes construir una vida que funcione sin él.</t>
+        </is>
+      </c>
+      <c r="G57" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H57" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones</t>
+        </is>
+      </c>
+      <c r="I57" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J57" s="20" t="inlineStr">
+        <is>
+          <t>59 s</t>
+        </is>
+      </c>
+      <c r="K57" s="20" t="inlineStr">
+        <is>
+          <t>Confrontación</t>
+        </is>
+      </c>
+      <c r="L57" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M57" s="24" t="n">
+        <v>8802</v>
+      </c>
+      <c r="N57" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O57" s="25">
+        <f>IFERROR(M57/N57,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P57" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q57" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-08-23-no-puedes-ser-realmente-feliz-con.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E58" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdNKSKZz1CI/</t>
+        </is>
+      </c>
+      <c r="F58" s="20" t="inlineStr">
+        <is>
+          <t>Muchas personas no se han dado cuenta que el verdadero trabajo no es hacer práctica tras práctica.</t>
+        </is>
+      </c>
+      <c r="G58" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H58" s="20" t="inlineStr">
+        <is>
+          <t>Espiritualidad / carencia</t>
+        </is>
+      </c>
+      <c r="I58" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J58" s="20" t="inlineStr">
+        <is>
+          <t>80 s</t>
+        </is>
+      </c>
+      <c r="K58" s="20" t="inlineStr">
+        <is>
+          <t>Confrontación</t>
+        </is>
+      </c>
+      <c r="L58" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M58" s="24" t="n">
+        <v>9780</v>
+      </c>
+      <c r="N58" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O58" s="25">
+        <f>IFERROR(M58/N58,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P58" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q58" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-12-el-hacer-desmedido-tambien-puede-ser.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>PsicoespacioVe</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="E59" s="23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/4326892114252564/</t>
+        </is>
+      </c>
+      <c r="F59" s="20" t="inlineStr">
+        <is>
+          <t>¿Qué pasaría si yo tomo mi bonsái chiquitito?</t>
+        </is>
+      </c>
+      <c r="G59" s="20" t="inlineStr">
+        <is>
+          <t>G7 · Metáfora visual</t>
+        </is>
+      </c>
+      <c r="H59" s="20" t="inlineStr">
+        <is>
+          <t>Identidad / potencial</t>
+        </is>
+      </c>
+      <c r="I59" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara + metáfora</t>
+        </is>
+      </c>
+      <c r="J59" s="20" t="inlineStr">
+        <is>
+          <t>77 s</t>
+        </is>
+      </c>
+      <c r="K59" s="20" t="inlineStr">
+        <is>
+          <t>Esperanza</t>
+        </is>
+      </c>
+      <c r="L59" s="20" t="inlineStr">
+        <is>
+          <t>Comenta PODER (programa $1,497)</t>
+        </is>
+      </c>
+      <c r="M59" s="24" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N59" s="24" t="n">
+        <v>2375</v>
+      </c>
+      <c r="O59" s="25">
+        <f>IFERROR(M59/N59,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P59" s="20" t="inlineStr">
+        <is>
+          <t>P6 · Historia o metáfora</t>
+        </is>
+      </c>
+      <c r="Q59" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/facebook-bonsai-maceta-grande.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E60" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc2ExiwMdkX/</t>
+        </is>
+      </c>
+      <c r="F60" s="20" t="inlineStr">
+        <is>
+          <t>Hay tres tipos de cerebros y probablemente el tuyo está en uno de estos tres niveles.</t>
+        </is>
+      </c>
+      <c r="G60" s="20" t="inlineStr">
+        <is>
+          <t>G5 · Lista</t>
+        </is>
+      </c>
+      <c r="H60" s="20" t="inlineStr">
+        <is>
+          <t>Mente / consciencia</t>
+        </is>
+      </c>
+      <c r="I60" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J60" s="20" t="inlineStr">
+        <is>
+          <t>53 s</t>
+        </is>
+      </c>
+      <c r="K60" s="20" t="inlineStr">
+        <is>
+          <t>Curiosidad</t>
+        </is>
+      </c>
+      <c r="L60" s="20" t="inlineStr">
+        <is>
+          <t>Pregunta: ¿en cuál estás?</t>
+        </is>
+      </c>
+      <c r="M60" s="24" t="n">
+        <v>8513</v>
+      </c>
+      <c r="N60" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O60" s="25">
+        <f>IFERROR(M60/N60,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P60" s="20" t="inlineStr">
+        <is>
+          <t>P5 · Lista o espejo de señales</t>
+        </is>
+      </c>
+      <c r="Q60" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-04-que-tipo-de-cerebro-tienes.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E61" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdFahcLNfg2/</t>
+        </is>
+      </c>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>Durante una gran parte de mi vida pensé que tenía que bajarle dos rayitas a quien era.</t>
+        </is>
+      </c>
+      <c r="G61" s="20" t="inlineStr">
+        <is>
+          <t>G11 · Historia / confesión</t>
+        </is>
+      </c>
+      <c r="H61" s="20" t="inlineStr">
+        <is>
+          <t>Neurodivergencia / sensibilidad</t>
+        </is>
+      </c>
+      <c r="I61" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara + historia</t>
+        </is>
+      </c>
+      <c r="J61" s="20" t="inlineStr">
+        <is>
+          <t>87 s</t>
+        </is>
+      </c>
+      <c r="K61" s="20" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="L61" s="20" t="inlineStr">
+        <is>
+          <t>Comenta RETO</t>
+        </is>
+      </c>
+      <c r="M61" s="24" t="n">
+        <v>7449</v>
+      </c>
+      <c r="N61" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O61" s="25">
+        <f>IFERROR(M61/N61,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P61" s="20" t="inlineStr">
+        <is>
+          <t>P6 · Historia o metáfora</t>
+        </is>
+      </c>
+      <c r="Q61" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-09-esta-es-la-realidad-de-muchas.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>PsicoespacioVe</t>
+        </is>
+      </c>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="E62" s="23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/2325501028218258/</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>Un buscador se levantó una mañana en su casa…</t>
+        </is>
+      </c>
+      <c r="G62" s="20" t="inlineStr">
+        <is>
+          <t>G7 · Metáfora / cuento</t>
+        </is>
+      </c>
+      <c r="H62" s="20" t="inlineStr">
+        <is>
+          <t>Propósito / miedo</t>
+        </is>
+      </c>
+      <c r="I62" s="20" t="inlineStr">
+        <is>
+          <t>Cuento narrado a cámara</t>
+        </is>
+      </c>
+      <c r="J62" s="20" t="inlineStr">
+        <is>
+          <t>167 s</t>
+        </is>
+      </c>
+      <c r="K62" s="20" t="inlineStr">
+        <is>
+          <t>Nostalgia / reflexión</t>
+        </is>
+      </c>
+      <c r="L62" s="20" t="inlineStr">
+        <is>
+          <t>Comenta PODER</t>
+        </is>
+      </c>
+      <c r="M62" s="24" t="n">
+        <v>4100</v>
+      </c>
+      <c r="N62" s="24" t="n">
+        <v>2375</v>
+      </c>
+      <c r="O62" s="25">
+        <f>IFERROR(M62/N62,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P62" s="20" t="inlineStr">
+        <is>
+          <t>P6 · Historia o metáfora</t>
+        </is>
+      </c>
+      <c r="Q62" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/facebook-el-unico-tiempo-que-de-verdad-viviste.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="E63" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dcm89nct3Mc/</t>
+        </is>
+      </c>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>Las ventas son 20% las palabras que dices y 80% la energía con que las dices.</t>
+        </is>
+      </c>
+      <c r="G63" s="20" t="inlineStr">
+        <is>
+          <t>G8 · Cifra</t>
+        </is>
+      </c>
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>Dinero / ventas</t>
+        </is>
+      </c>
+      <c r="I63" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J63" s="20" t="inlineStr">
+        <is>
+          <t>60 s</t>
+        </is>
+      </c>
+      <c r="K63" s="20" t="inlineStr">
+        <is>
+          <t>Curiosidad</t>
+        </is>
+      </c>
+      <c r="L63" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M63" s="24" t="n">
+        <v>6998</v>
+      </c>
+      <c r="N63" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O63" s="25">
+        <f>IFERROR(M63/N63,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P63" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q63" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-08-29-estas-son-las-6-ensenanzas-de.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E64" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dd5JvoGtoFC/</t>
+        </is>
+      </c>
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>Si tienes TDAH, deja de intentar construir tu vida alrededor de cosas que no te estimulan.</t>
+        </is>
+      </c>
+      <c r="G64" s="20" t="inlineStr">
+        <is>
+          <t>G2 · Consejo práctico</t>
+        </is>
+      </c>
+      <c r="H64" s="20" t="inlineStr">
+        <is>
+          <t>TDAH / propósito</t>
+        </is>
+      </c>
+      <c r="I64" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J64" s="20" t="inlineStr">
+        <is>
+          <t>77 s</t>
+        </is>
+      </c>
+      <c r="K64" s="20" t="inlineStr">
+        <is>
+          <t>Alivio</t>
+        </is>
+      </c>
+      <c r="L64" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M64" s="24" t="n">
+        <v>6909</v>
+      </c>
+      <c r="N64" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O64" s="25">
+        <f>IFERROR(M64/N64,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P64" s="20" t="inlineStr">
+        <is>
+          <t>P2 · Herramienta para usar ya (decreto, ritual, técnica)</t>
+        </is>
+      </c>
+      <c r="Q64" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-30-si-tienes-tdah-este-consejo-cambiara.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="20" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="inlineStr">
+        <is>
+          <t>PsicoespacioVe</t>
+        </is>
+      </c>
+      <c r="D65" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="E65" s="23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/2931408003895018/</t>
+        </is>
+      </c>
+      <c r="F65" s="20" t="inlineStr">
+        <is>
+          <t>…solo quieres rezar para que algo más grande que tú te traiga el resultado: no va a funcionar.</t>
+        </is>
+      </c>
+      <c r="G65" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H65" s="20" t="inlineStr">
+        <is>
+          <t>Espiritualidad / acción</t>
+        </is>
+      </c>
+      <c r="I65" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara (fragmento de clase)</t>
+        </is>
+      </c>
+      <c r="J65" s="20" t="inlineStr">
+        <is>
+          <t>56 s</t>
+        </is>
+      </c>
+      <c r="K65" s="20" t="inlineStr">
+        <is>
+          <t>Confrontación</t>
+        </is>
+      </c>
+      <c r="L65" s="20" t="inlineStr">
+        <is>
+          <t>Comenta CLASE</t>
+        </is>
+      </c>
+      <c r="M65" s="24" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N65" s="24" t="n">
+        <v>2375</v>
+      </c>
+      <c r="O65" s="25">
+        <f>IFERROR(M65/N65,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P65" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q65" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/facebook-oras-y-no-actuas.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D66" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E66" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdAb5lMNKk5/</t>
+        </is>
+      </c>
+      <c r="F66" s="20" t="inlineStr">
+        <is>
+          <t>Carl Jung dijo una vez: hasta que hagas consciente lo inconsciente, dirigirá tu vida…</t>
+        </is>
+      </c>
+      <c r="G66" s="20" t="inlineStr">
+        <is>
+          <t>G6 · Cita</t>
+        </is>
+      </c>
+      <c r="H66" s="20" t="inlineStr">
+        <is>
+          <t>Dinero / subconsciente</t>
+        </is>
+      </c>
+      <c r="I66" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara + historia</t>
+        </is>
+      </c>
+      <c r="J66" s="20" t="inlineStr">
+        <is>
+          <t>86 s</t>
+        </is>
+      </c>
+      <c r="K66" s="20" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="L66" s="20" t="inlineStr">
+        <is>
+          <t>Reto 15 de septiembre</t>
+        </is>
+      </c>
+      <c r="M66" s="24" t="n">
+        <v>6551</v>
+      </c>
+      <c r="N66" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O66" s="25">
+        <f>IFERROR(M66/N66,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P66" s="20" t="inlineStr">
+        <is>
+          <t>P7 · Autoridad: estudio, famoso o cita</t>
+        </is>
+      </c>
+      <c r="Q66" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-08-hasta-que-hagas-consciente-lo-inconsciente.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C67" s="20" t="inlineStr">
+        <is>
+          <t>PsicoespacioVe</t>
+        </is>
+      </c>
+      <c r="D67" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="E67" s="23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/1606172144251021/</t>
+        </is>
+      </c>
+      <c r="F67" s="20" t="inlineStr">
+        <is>
+          <t>Para que dos personas sean pareja de verdad tienen que tener…</t>
+        </is>
+      </c>
+      <c r="G67" s="20" t="inlineStr">
+        <is>
+          <t>G5 · Espejo / lista</t>
+        </is>
+      </c>
+      <c r="H67" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones</t>
+        </is>
+      </c>
+      <c r="I67" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara (fragmento de clase)</t>
+        </is>
+      </c>
+      <c r="J67" s="20" t="inlineStr">
+        <is>
+          <t>66 s</t>
+        </is>
+      </c>
+      <c r="K67" s="20" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="L67" s="20" t="inlineStr">
+        <is>
+          <t>Comenta REPROGRÁMATE (clases gratis)</t>
+        </is>
+      </c>
+      <c r="M67" s="24" t="n">
+        <v>3800</v>
+      </c>
+      <c r="N67" s="24" t="n">
+        <v>2375</v>
+      </c>
+      <c r="O67" s="25">
+        <f>IFERROR(M67/N67,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P67" s="20" t="inlineStr">
+        <is>
+          <t>P5 · Lista o espejo de señales</t>
+        </is>
+      </c>
+      <c r="Q67" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/facebook-es-un-socio-no-una-pareja.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="20" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E68" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DckT247NWAd/</t>
+        </is>
+      </c>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>Manifiesto que este video solo le aparezca a la mujer que está destinada a ser realmente exitosa.</t>
+        </is>
+      </c>
+      <c r="G68" s="20" t="inlineStr">
+        <is>
+          <t>G11 · Historia / confesión</t>
+        </is>
+      </c>
+      <c r="H68" s="20" t="inlineStr">
+        <is>
+          <t>Metas / éxito</t>
+        </is>
+      </c>
+      <c r="I68" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara + historia</t>
+        </is>
+      </c>
+      <c r="J68" s="20" t="inlineStr">
+        <is>
+          <t>79 s</t>
+        </is>
+      </c>
+      <c r="K68" s="20" t="inlineStr">
+        <is>
+          <t>Esperanza</t>
+        </is>
+      </c>
+      <c r="L68" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M68" s="24" t="n">
+        <v>5693</v>
+      </c>
+      <c r="N68" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O68" s="28">
+        <f>IFERROR(M68/N68,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P68" s="20" t="inlineStr">
+        <is>
+          <t>P6 · Historia o metáfora</t>
+        </is>
+      </c>
+      <c r="Q68" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-08-28-si-estas-viendo-esto-es-por.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C69" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D69" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="E69" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc7ZDExjQPf/</t>
+        </is>
+      </c>
+      <c r="F69" s="20" t="inlineStr">
+        <is>
+          <t>(caption) Demasiado PODER para el sistema equivocado!</t>
+        </is>
+      </c>
+      <c r="G69" s="20" t="inlineStr">
+        <is>
+          <t>Anuncio</t>
+        </is>
+      </c>
+      <c r="H69" s="20" t="inlineStr">
+        <is>
+          <t>TDAH / reto</t>
+        </is>
+      </c>
+      <c r="I69" s="20" t="inlineStr">
+        <is>
+          <t>En vivo (sin transcripción)</t>
+        </is>
+      </c>
+      <c r="J69" s="20" t="inlineStr">
+        <is>
+          <t>s/d s</t>
+        </is>
+      </c>
+      <c r="K69" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="L69" s="20" t="inlineStr">
+        <is>
+          <t>Link en bio</t>
+        </is>
+      </c>
+      <c r="M69" s="24" t="n">
+        <v>5432</v>
+      </c>
+      <c r="N69" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O69" s="28">
+        <f>IFERROR(M69/N69,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P69" s="20" t="inlineStr">
+        <is>
+          <t>P8 · Anuncio directo de evento o producto</t>
+        </is>
+      </c>
+      <c r="Q69" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-06-demasiado-poder-para-el-sistema-equivocado.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="20" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E70" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdkOiAts4IT/</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>Lo que no enfrentas no desaparece, solo aprendes a esconderlo mejor.</t>
+        </is>
+      </c>
+      <c r="G70" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H70" s="20" t="inlineStr">
+        <is>
+          <t>Perfeccionismo</t>
+        </is>
+      </c>
+      <c r="I70" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J70" s="20" t="inlineStr">
+        <is>
+          <t>73 s</t>
+        </is>
+      </c>
+      <c r="K70" s="20" t="inlineStr">
+        <is>
+          <t>Confrontación</t>
+        </is>
+      </c>
+      <c r="L70" s="20" t="inlineStr">
+        <is>
+          <t>Comenta PODER</t>
+        </is>
+      </c>
+      <c r="M70" s="24" t="n">
+        <v>5291</v>
+      </c>
+      <c r="N70" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O70" s="28">
+        <f>IFERROR(M70/N70,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P70" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q70" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-21-comenta-poder-y-te-lo-envio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="20" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C71" s="20" t="inlineStr">
+        <is>
+          <t>PsicoespacioVe</t>
+        </is>
+      </c>
+      <c r="D71" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="E71" s="23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/1609978707244310/</t>
+        </is>
+      </c>
+      <c r="F71" s="20" t="inlineStr">
+        <is>
+          <t>Muchísimas mujeres escriben a diario: tienen más de 10 años aceptando migajas…</t>
+        </is>
+      </c>
+      <c r="G71" s="20" t="inlineStr">
+        <is>
+          <t>G4 · Pregunta-dolor</t>
+        </is>
+      </c>
+      <c r="H71" s="20" t="inlineStr">
+        <is>
+          <t>Relaciones</t>
+        </is>
+      </c>
+      <c r="I71" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J71" s="20" t="inlineStr">
+        <is>
+          <t>59 s</t>
+        </is>
+      </c>
+      <c r="K71" s="20" t="inlineStr">
+        <is>
+          <t>Identificación</t>
+        </is>
+      </c>
+      <c r="L71" s="20" t="inlineStr">
+        <is>
+          <t>Comenta CAMBIO</t>
+        </is>
+      </c>
+      <c r="M71" s="24" t="n">
+        <v>2900</v>
+      </c>
+      <c r="N71" s="24" t="n">
+        <v>2375</v>
+      </c>
+      <c r="O71" s="28">
+        <f>IFERROR(M71/N71,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P71" s="20" t="inlineStr">
+        <is>
+          <t>P3 · Dolor en sus palabras + explicación</t>
+        </is>
+      </c>
+      <c r="Q71" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/facebook-que-concepto-de-amor-aprendiste.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="20" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E72" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DeIfmHJNQW8/</t>
+        </is>
+      </c>
+      <c r="F72" s="20" t="inlineStr">
+        <is>
+          <t>Hay una razón por la que tu cerebro sigue obsesionándose con las cosas que empezaste pero no terminas.</t>
+        </is>
+      </c>
+      <c r="G72" s="20" t="inlineStr">
+        <is>
+          <t>G6 · Autoridad (Zeigarnik)</t>
+        </is>
+      </c>
+      <c r="H72" s="20" t="inlineStr">
+        <is>
+          <t>Ansiedad / mente saturada</t>
+        </is>
+      </c>
+      <c r="I72" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J72" s="20" t="inlineStr">
+        <is>
+          <t>71 s</t>
+        </is>
+      </c>
+      <c r="K72" s="20" t="inlineStr">
+        <is>
+          <t>Alivio</t>
+        </is>
+      </c>
+      <c r="L72" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M72" s="24" t="n">
+        <v>4684</v>
+      </c>
+      <c r="N72" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O72" s="28">
+        <f>IFERROR(M72/N72,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P72" s="20" t="inlineStr">
+        <is>
+          <t>P7 · Autoridad: estudio, famoso o cita</t>
+        </is>
+      </c>
+      <c r="Q72" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-10-06-el-truco-mental-que-la-mayoria.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="20" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E73" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcPlgPnNYrC/</t>
+        </is>
+      </c>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>Eso que llamas ambición muchas veces es miedo al fracaso.</t>
+        </is>
+      </c>
+      <c r="G73" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>Metas / éxito</t>
+        </is>
+      </c>
+      <c r="I73" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J73" s="20" t="inlineStr">
+        <is>
+          <t>71 s</t>
+        </is>
+      </c>
+      <c r="K73" s="20" t="inlineStr">
+        <is>
+          <t>Sorpresa</t>
+        </is>
+      </c>
+      <c r="L73" s="20" t="inlineStr">
+        <is>
+          <t>Comenta PODCAST</t>
+        </is>
+      </c>
+      <c r="M73" s="24" t="n">
+        <v>4653</v>
+      </c>
+      <c r="N73" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O73" s="28">
+        <f>IFERROR(M73/N73,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P73" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q73" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-08-20-eso-que-llamas-ambicion-muchas-veces.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="20" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="inlineStr">
+        <is>
+          <t>@quantumquip</t>
+        </is>
+      </c>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E74" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DcwRsbCJK3Y/</t>
+        </is>
+      </c>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>Y este niño interno tuvo que sacar ciertas conclusiones para sobrevivir…</t>
+        </is>
+      </c>
+      <c r="G74" s="20" t="inlineStr">
+        <is>
+          <t>Fragmento de podcast</t>
+        </is>
+      </c>
+      <c r="H74" s="20" t="inlineStr">
+        <is>
+          <t>Niño interno</t>
+        </is>
+      </c>
+      <c r="I74" s="20" t="inlineStr">
+        <is>
+          <t>Corte de podcast</t>
+        </is>
+      </c>
+      <c r="J74" s="20" t="inlineStr">
+        <is>
+          <t>42 s</t>
+        </is>
+      </c>
+      <c r="K74" s="20" t="inlineStr">
+        <is>
+          <t>Comprensión</t>
+        </is>
+      </c>
+      <c r="L74" s="20" t="inlineStr">
+        <is>
+          <t>Episodio nuevo</t>
+        </is>
+      </c>
+      <c r="M74" s="24" t="n">
+        <v>5093</v>
+      </c>
+      <c r="N74" s="24" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O74" s="28">
+        <f>IFERROR(M74/N74,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P74" s="20" t="inlineStr">
+        <is>
+          <t>P3 · Dolor en sus palabras + explicación</t>
+        </is>
+      </c>
+      <c r="Q74" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-01-hay-nuevo-episodio-quieres-ir-a.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="20" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D75" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="E75" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DeA8R_KKKho/</t>
+        </is>
+      </c>
+      <c r="F75" s="20" t="inlineStr">
+        <is>
+          <t>La paz interior es la nueva riqueza.</t>
+        </is>
+      </c>
+      <c r="G75" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H75" s="20" t="inlineStr">
+        <is>
+          <t>Paz / abundancia</t>
+        </is>
+      </c>
+      <c r="I75" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J75" s="20" t="inlineStr">
+        <is>
+          <t>60 s</t>
+        </is>
+      </c>
+      <c r="K75" s="20" t="inlineStr">
+        <is>
+          <t>Calma</t>
+        </is>
+      </c>
+      <c r="L75" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M75" s="24" t="n">
+        <v>4291</v>
+      </c>
+      <c r="N75" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O75" s="28">
+        <f>IFERROR(M75/N75,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P75" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q75" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-10-03-la-paz-interior-es-la-nueva.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E76" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DeGCZ3qNgSw/</t>
+        </is>
+      </c>
+      <c r="F76" s="20" t="inlineStr">
+        <is>
+          <t>La mayoría de las personas no están atrapadas en su realidad, están atrapadas en la interpretación que hicieron de ella.</t>
+        </is>
+      </c>
+      <c r="G76" s="20" t="inlineStr">
+        <is>
+          <t>G1 · Reencuadre</t>
+        </is>
+      </c>
+      <c r="H76" s="20" t="inlineStr">
+        <is>
+          <t>Mente / percepción</t>
+        </is>
+      </c>
+      <c r="I76" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara</t>
+        </is>
+      </c>
+      <c r="J76" s="20" t="inlineStr">
+        <is>
+          <t>47 s</t>
+        </is>
+      </c>
+      <c r="K76" s="20" t="inlineStr">
+        <is>
+          <t>Sorpresa</t>
+        </is>
+      </c>
+      <c r="L76" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="M76" s="24" t="n">
+        <v>4085</v>
+      </c>
+      <c r="N76" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O76" s="28">
+        <f>IFERROR(M76/N76,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P76" s="20" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="Q76" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-10-05-las-personas-no-estan-atrapadas-en.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="20" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D77" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E77" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdcwFDrDfQV/</t>
+        </is>
+      </c>
+      <c r="F77" s="20" t="inlineStr">
+        <is>
+          <t>(caption) Neurospicys al P.O.D.E.R. comenzamos el 24 de septiembre</t>
+        </is>
+      </c>
+      <c r="G77" s="20" t="inlineStr">
+        <is>
+          <t>Anuncio</t>
+        </is>
+      </c>
+      <c r="H77" s="20" t="inlineStr">
+        <is>
+          <t>TDAH / reto</t>
+        </is>
+      </c>
+      <c r="I77" s="20" t="inlineStr">
+        <is>
+          <t>En vivo (sin transcripción)</t>
+        </is>
+      </c>
+      <c r="J77" s="20" t="inlineStr">
+        <is>
+          <t>s/d s</t>
+        </is>
+      </c>
+      <c r="K77" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="L77" s="20" t="inlineStr">
+        <is>
+          <t>Link en bio</t>
+        </is>
+      </c>
+      <c r="M77" s="24" t="n">
+        <v>3531</v>
+      </c>
+      <c r="N77" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O77" s="28">
+        <f>IFERROR(M77/N77,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P77" s="20" t="inlineStr">
+        <is>
+          <t>P8 · Anuncio directo de evento o producto</t>
+        </is>
+      </c>
+      <c r="Q77" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-19-neurospicys-al-p-o-d-e.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="20" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E78" s="23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdsI9-ZN8wT/</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>Durante años me hicieron sentir que hablaba demasiado. Hoy hago millones hablando.</t>
+        </is>
+      </c>
+      <c r="G78" s="20" t="inlineStr">
+        <is>
+          <t>G11 · Historia / confesión</t>
+        </is>
+      </c>
+      <c r="H78" s="20" t="inlineStr">
+        <is>
+          <t>Identidad / dinero</t>
+        </is>
+      </c>
+      <c r="I78" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara + historia</t>
+        </is>
+      </c>
+      <c r="J78" s="20" t="inlineStr">
+        <is>
+          <t>89 s</t>
+        </is>
+      </c>
+      <c r="K78" s="20" t="inlineStr">
+        <is>
+          <t>Inspiración</t>
+        </is>
+      </c>
+      <c r="L78" s="20" t="inlineStr">
+        <is>
+          <t>Comenta PODER</t>
+        </is>
+      </c>
+      <c r="M78" s="24" t="n">
+        <v>3194</v>
+      </c>
+      <c r="N78" s="24" t="n">
+        <v>4071.5</v>
+      </c>
+      <c r="O78" s="28">
+        <f>IFERROR(M78/N78,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P78" s="20" t="inlineStr">
+        <is>
+          <t>P6 · Historia o metáfora</t>
+        </is>
+      </c>
+      <c r="Q78" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/instagram-2026-09-25-te-cuento-una-parte-de-mi.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="20" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="inlineStr">
+        <is>
+          <t>PsicoespacioVe</t>
+        </is>
+      </c>
+      <c r="D79" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="E79" s="23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/2720591191671210/</t>
+        </is>
+      </c>
+      <c r="F79" s="20" t="inlineStr">
+        <is>
+          <t>Mañana empezamos, mi gente bella: 4 clases que te van a abrir los ojos…</t>
+        </is>
+      </c>
+      <c r="G79" s="20" t="inlineStr">
+        <is>
+          <t>Anuncio</t>
+        </is>
+      </c>
+      <c r="H79" s="20" t="inlineStr">
+        <is>
+          <t>Patrones repetidos</t>
+        </is>
+      </c>
+      <c r="I79" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara corto</t>
+        </is>
+      </c>
+      <c r="J79" s="20" t="inlineStr">
+        <is>
+          <t>28 s</t>
+        </is>
+      </c>
+      <c r="K79" s="20" t="inlineStr">
+        <is>
+          <t>Urgencia</t>
+        </is>
+      </c>
+      <c r="L79" s="20" t="inlineStr">
+        <is>
+          <t>Inscríbete (WhatsApp / link en perfil)</t>
+        </is>
+      </c>
+      <c r="M79" s="24" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N79" s="24" t="n">
+        <v>2375</v>
+      </c>
+      <c r="O79" s="28">
+        <f>IFERROR(M79/N79,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P79" s="20" t="inlineStr">
+        <is>
+          <t>P8 · Anuncio directo de evento o producto</t>
+        </is>
+      </c>
+      <c r="Q79" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/facebook-cuatro-clases-gratuitas-manana-empezamos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr">
+        <is>
+          <t>PsicoespacioVe</t>
+        </is>
+      </c>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="E80" s="23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/1897028914817172/</t>
+        </is>
+      </c>
+      <c r="F80" s="20" t="inlineStr">
+        <is>
+          <t>Acabamos de terminar la primera clase de Reprográmate…</t>
+        </is>
+      </c>
+      <c r="G80" s="20" t="inlineStr">
+        <is>
+          <t>Anuncio</t>
+        </is>
+      </c>
+      <c r="H80" s="20" t="inlineStr">
+        <is>
+          <t>Patrones repetidos</t>
+        </is>
+      </c>
+      <c r="I80" s="20" t="inlineStr">
+        <is>
+          <t>Cara a cámara corto</t>
+        </is>
+      </c>
+      <c r="J80" s="20" t="inlineStr">
+        <is>
+          <t>44 s</t>
+        </is>
+      </c>
+      <c r="K80" s="20" t="inlineStr">
+        <is>
+          <t>Urgencia</t>
+        </is>
+      </c>
+      <c r="L80" s="20" t="inlineStr">
+        <is>
+          <t>Comenta CLASE (repetición)</t>
+        </is>
+      </c>
+      <c r="M80" s="24" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="N80" s="24" t="n">
+        <v>2375</v>
+      </c>
+      <c r="O80" s="28">
+        <f>IFERROR(M80/N80,"s/d")</f>
+        <v/>
+      </c>
+      <c r="P80" s="20" t="inlineStr">
+        <is>
+          <t>P8 · Anuncio directo de evento o producto</t>
+        </is>
+      </c>
+      <c r="Q80" s="20" t="inlineStr">
+        <is>
+          <t>transcripciones/facebook-terminamos-la-primera-clase-reprogramate.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>Fuentes y supuestos:</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="29" t="inlineStr">
+        <is>
+          <t>Vistas: de cada transcripción (Apify / vidIQ). En Facebook son las que muestra el título del reel (ej. "46K").</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="29" t="inlineStr">
+        <is>
+          <t>Mediana de la cuenta: @mabradiante = 11,850 (mediana de 40 TikToks); @manifestadoras = 674,000 (mediana de 40 TikToks); @soylizadebri = 1,500,000 (mediana de 40 TikToks); @transformacion_acelerada = 295,900 (mediana de 40 TikToks); @danielacorreaup = 4,072 (mediana de 36 reels); @quantumquip = 4,530 (mediana de 14 reels); PsicoespacioVe = 2,375 (mediana de 27 posts con vistas). Sale de fuentes/*.json (recolección del 2026-10-06).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="29" t="inlineStr">
+        <is>
+          <t>Verde = más de 1.5x (le fue mucho mejor de lo normal para esa cuenta). Rojo = menos de 0.7x. Morado = tus propios videos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="29" t="inlineStr">
+        <is>
+          <t>OJO: transcribimos sobre todo los videos MÁS vistos de cada cuenta, así que casi todo sale arriba de 1.5x. Sirve para ver qué tienen en común los virales; no para decir qué fracasa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="29" t="inlineStr">
+        <is>
+          <t>Hook, tipo, tema, formato, emoción, CTA y patrón: clasificación de NICA leyendo cada transcripción. Donde no hay voz, el hook sale del caption y se marca "(caption)" o "(texto en pantalla)".</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q80"/>
+  <mergeCells count="5">
+    <mergeCell ref="A86:L86"/>
+    <mergeCell ref="A85:L85"/>
+    <mergeCell ref="A84:L84"/>
+    <mergeCell ref="A83:L83"/>
+    <mergeCell ref="A87:L87"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId79"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>PATRÓN</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Piezas</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Rendimiento típico (mediana)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Arriba de 1.5x</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Abajo de 0.7x</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Ejemplo real</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>P2 · Herramienta para usar ya (decreto, ritual, técnica)</t>
+        </is>
+      </c>
+      <c r="B2" s="20">
+        <f>COUNTIF(Competencia!$P$2:$P$80,A2)</f>
+        <v/>
+      </c>
+      <c r="C2" s="30" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A2,Competencia!$O$2:$O$80,"&gt;1.5")</f>
+        <v/>
+      </c>
+      <c r="E2" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A2,Competencia!$O$2:$O$80,"&lt;0.7")</f>
+        <v/>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>@mabradiante: "Di esto en tu casa y mira cómo todo comienza a cambiar." (186x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>P5 · Lista o espejo de señales</t>
+        </is>
+      </c>
+      <c r="B3" s="20">
+        <f>COUNTIF(Competencia!$P$2:$P$80,A3)</f>
+        <v/>
+      </c>
+      <c r="C3" s="30" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="D3" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A3,Competencia!$O$2:$O$80,"&gt;1.5")</f>
+        <v/>
+      </c>
+      <c r="E3" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A3,Competencia!$O$2:$O$80,"&lt;0.7")</f>
+        <v/>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup: "Odian los ruidos fuertes, pero pueden escuchar la misma canción durante cinco horas." (532x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>P7 · Autoridad: estudio, famoso o cita</t>
+        </is>
+      </c>
+      <c r="B4" s="20">
+        <f>COUNTIF(Competencia!$P$2:$P$80,A4)</f>
+        <v/>
+      </c>
+      <c r="C4" s="30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D4" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A4,Competencia!$O$2:$O$80,"&gt;1.5")</f>
+        <v/>
+      </c>
+      <c r="E4" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A4,Competencia!$O$2:$O$80,"&lt;0.7")</f>
+        <v/>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup: "Sabrina Carpenter es el ejemplo perfecto de cómo funciona la manifestación." (35x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>P9 · Texto en pantalla + música (sin voz)</t>
+        </is>
+      </c>
+      <c r="B5" s="20">
+        <f>COUNTIF(Competencia!$P$2:$P$80,A5)</f>
+        <v/>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D5" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A5,Competencia!$O$2:$O$80,"&gt;1.5")</f>
+        <v/>
+      </c>
+      <c r="E5" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A5,Competencia!$O$2:$O$80,"&lt;0.7")</f>
+        <v/>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup: "(texto en pantalla) La física ya lo confirmó: lo que no puedes ver es lo que construye tod" (136x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>P4 · Reacción a video ajeno de dolor o polémica</t>
+        </is>
+      </c>
+      <c r="B6" s="20">
+        <f>COUNTIF(Competencia!$P$2:$P$80,A6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D6" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A6,Competencia!$O$2:$O$80,"&gt;1.5")</f>
+        <v/>
+      </c>
+      <c r="E6" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A6,Competencia!$O$2:$O$80,"&lt;0.7")</f>
+        <v/>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>@transformacion_acelerada: "Te lo digo crudo y sin rodeos." (3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>P1 · Romper creencia + nombre propio al problema</t>
+        </is>
+      </c>
+      <c r="B7" s="20">
+        <f>COUNTIF(Competencia!$P$2:$P$80,A7)</f>
+        <v/>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D7" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A7,Competencia!$O$2:$O$80,"&gt;1.5")</f>
+        <v/>
+      </c>
+      <c r="E7" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A7,Competencia!$O$2:$O$80,"&lt;0.7")</f>
+        <v/>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup: "Las personas con TDAH no tienen un déficit de atención, tienen un exceso de atención para " (614x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>P3 · Dolor en sus palabras + explicación</t>
+        </is>
+      </c>
+      <c r="B8" s="20">
+        <f>COUNTIF(Competencia!$P$2:$P$80,A8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D8" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A8,Competencia!$O$2:$O$80,"&gt;1.5")</f>
+        <v/>
+      </c>
+      <c r="E8" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A8,Competencia!$O$2:$O$80,"&lt;0.7")</f>
+        <v/>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>@danielacorreaup: "¿Cómo sabes si realmente tienes TDAH o simplemente estás distraído?" (11x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>P6 · Historia o metáfora</t>
+        </is>
+      </c>
+      <c r="B9" s="20">
+        <f>COUNTIF(Competencia!$P$2:$P$80,A9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D9" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A9,Competencia!$O$2:$O$80,"&gt;1.5")</f>
+        <v/>
+      </c>
+      <c r="E9" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A9,Competencia!$O$2:$O$80,"&lt;0.7")</f>
+        <v/>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>PsicoespacioVe: "Los bonsáis no simplemente son árboles que nacieron enanos." (14x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>P8 · Anuncio directo de evento o producto</t>
+        </is>
+      </c>
+      <c r="B10" s="20">
+        <f>COUNTIF(Competencia!$P$2:$P$80,A10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D10" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A10,Competencia!$O$2:$O$80,"&gt;1.5")</f>
+        <v/>
+      </c>
+      <c r="E10" s="20">
+        <f>COUNTIFS(Competencia!$P$2:$P$80,A10,Competencia!$O$2:$O$80,"&lt;0.7")</f>
+        <v/>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>PsicoespacioVe: "Les voy a dar un regalo… hay un programa gratuito…" (6x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>La mediana la calculé con las vistas de la pestaña Competencia (es un valor fijo; si agregas filas, se recalcula en la rutina semanal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>QUÉ FUNCIONA (piezas arriba de 1.5x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>• Herramienta para usar ya (P2): 8 de 8 piezas arriba de 1.5x, rendimiento típico 26x. Aquí están tus 4 videos más vistos ("Di esto en tu casa…", "Cuidado con este video…").</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>• Lista o espejo de señales (P5): 6 de 6 arriba, 8.9x. Ej.: "Odian los ruidos fuertes, pero…" (2.2M en Instagram).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>• Autoridad: estudio, famoso o cita (P7): 6 de 7 arriba, 7.6x. Ej.: Sabrina Carpenter, Lady Gaga, Harvard, Carl Jung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>• Relaciones es el tema con más piezas virales (16) y las vistas más altas en TikTok (de 1 a 7.2 millones).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>• TDAH / neurodivergencia: 10 piezas, rendimiento típico 13x (cuenta @danielacorreaup). Tú tienes TDAH: es tu historia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>QUÉ NO FUNCIONA (piezas abajo de 0.7x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>• Casi no hay datos: transcribimos los videos más vistos, así que ninguna pieza quedó abajo de 0.7x. Lo más bajo fue:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>• Anuncio directo de evento o producto (P8): rendimiento típico 1.1x, el más bajo de todos. Ej.: "Mañana empezamos: 4 clases…" (0.7x).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>• Historias personales largas (P6): 1.8x. Funcionan, pero menos que la herramienta o la lista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>• Piezas que piden "comenta para el link": 2.4x contra 4.7x de las que no venden. Vender recorta alcance: por eso solo 1 de 3 piezas al día vende.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>EL PATRÓN DE VIRALIDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>• Gancho que nombra el dolor o rompe una creencia → algo concreto para usar YA (decreto, ritual, lista de señales) → cierre corto. La venta, solo en 1 de cada 3 piezas y al final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>LO QUE NO SABEMOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>• Qué falla: nos faltan videos de bajo rendimiento transcritos para comparar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>• Lo que dicen los 12 reels de @quantumquip y los 2 de @danielacorreaup que son solo texto en pantalla + música: tenemos el caption, no el texto exacto en pantalla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>• YouTube: el canal estudiado está en inglés y no tiene transcripciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>• Tus números en Instagram, Facebook y YouTube: todavía no los medimos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>• Retención (hasta qué segundo ven): ninguna fuente la da públicamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>3 HALLAZGOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>• 1. Tu arma más fuerte es la HERRAMIENTA PARA USAR YA: 8 de 8 piezas virales, 26x típico, y ahí están tus 4 videos más vistos. Mínimo 1 por día (ya está en el calendario: pieza 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>• 2. "Romper creencia" es el gancho más usado (25 piezas) pero rinde menos (2.7x) que la LISTA DE SEÑALES (8.9x) o un FAMOSO / ESTUDIO (7.6x). Combínalo: "No es que no te elijan… y estas son las 3 señales".</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>• 3. RELACIONES es el tema con más virales del nicho y TDAH rinde 13x: los dos son tu terreno (Querido Ex y tu historia con TDAH).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>